--- a/MACC_KZ_29052026_rev.xlsx
+++ b/MACC_KZ_29052026_rev.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Development\MACC online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3ED27B5-A731-4CF0-B728-7840230EA2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59388B2E-57E7-4444-8CF9-A97007FC8628}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18570" yWindow="2120" windowWidth="18250" windowHeight="16870" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MACC" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="671">
   <si>
     <t>ПРЕДПОСЫЛКИ</t>
   </si>
@@ -2050,6 +2050,15 @@
   </si>
   <si>
     <t>Выбросы сектора</t>
+  </si>
+  <si>
+    <t>Уд. CAPEX модернизации электросетей</t>
+  </si>
+  <si>
+    <t>Уд. CAPEX модернизации завода</t>
+  </si>
+  <si>
+    <t>Уд. CAPEX модернизации очистных</t>
   </si>
 </sst>
 </file>
@@ -2559,10 +2568,10 @@
     <xf numFmtId="1" fontId="32" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="32" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2935,7 +2944,7 @@
       </c>
       <c r="H6" s="11">
         <f>Расчёты!C673</f>
-        <v>4280</v>
+        <v>1160</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" ref="I6:I31" si="0">E6-PV($C$2,G6,F6)</f>
@@ -2943,11 +2952,11 @@
       </c>
       <c r="J6" s="11">
         <f t="shared" ref="J6:J31" si="1">-PV($C$2,G6,H6)</f>
-        <v>24182.954561598515</v>
+        <v>6554.2587129566055</v>
       </c>
       <c r="K6" s="9">
         <f t="shared" ref="K6:K32" si="2">IF(J6=0,0,I6/J6*1000)</f>
-        <v>-7.9773015072962767</v>
+        <v>-29.433491768300062</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2977,7 +2986,7 @@
       </c>
       <c r="H7" s="11">
         <f>Расчёты!C697</f>
-        <v>2140</v>
+        <v>580</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="0"/>
@@ -2985,11 +2994,11 @@
       </c>
       <c r="J7" s="11">
         <f t="shared" si="1"/>
-        <v>15984.609356061057</v>
+        <v>4332.2773021100065</v>
       </c>
       <c r="K7" s="9">
         <f t="shared" si="2"/>
-        <v>-6.8261124256439487</v>
+        <v>-25.186001018755256</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3145,7 +3154,7 @@
       </c>
       <c r="H11" s="111">
         <f>Расчёты!C649</f>
-        <v>3424</v>
+        <v>264</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="0"/>
@@ -3153,11 +3162,11 @@
       </c>
       <c r="J11" s="11">
         <f t="shared" si="1"/>
-        <v>23320.400011928181</v>
+        <v>1798.0682252187614</v>
       </c>
       <c r="K11" s="9">
         <f t="shared" si="2"/>
-        <v>9.067544361537351</v>
+        <v>117.60330262842383</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4010,7 +4019,7 @@
       </c>
       <c r="H32" s="14">
         <f>SUM(H6:H31)</f>
-        <v>222192.91897671297</v>
+        <v>214352.91897671297</v>
       </c>
       <c r="I32" s="14">
         <f>SUM(I6:I31)</f>
@@ -4018,11 +4027,11 @@
       </c>
       <c r="J32" s="14">
         <f>SUM(J6:J31)</f>
-        <v>1701684.9254739543</v>
+        <v>1650881.565784652</v>
       </c>
       <c r="K32" s="15">
         <f t="shared" si="2"/>
-        <v>92.726465453923396</v>
+        <v>95.579980857334135</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
@@ -4348,15 +4357,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="112" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
@@ -5021,70 +5030,70 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" s="112" t="s">
+      <c r="A36" s="113" t="s">
         <v>178</v>
       </c>
-      <c r="B36" s="112"/>
-      <c r="C36" s="112"/>
-      <c r="D36" s="112"/>
-      <c r="E36" s="112"/>
-      <c r="F36" s="112"/>
-      <c r="G36" s="112"/>
+      <c r="B36" s="113"/>
+      <c r="C36" s="113"/>
+      <c r="D36" s="113"/>
+      <c r="E36" s="113"/>
+      <c r="F36" s="113"/>
+      <c r="G36" s="113"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="112" t="s">
+      <c r="A37" s="113" t="s">
         <v>179</v>
       </c>
-      <c r="B37" s="112"/>
-      <c r="C37" s="112"/>
-      <c r="D37" s="112"/>
-      <c r="E37" s="112"/>
-      <c r="F37" s="112"/>
-      <c r="G37" s="112"/>
+      <c r="B37" s="113"/>
+      <c r="C37" s="113"/>
+      <c r="D37" s="113"/>
+      <c r="E37" s="113"/>
+      <c r="F37" s="113"/>
+      <c r="G37" s="113"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="112" t="s">
+      <c r="A38" s="113" t="s">
         <v>180</v>
       </c>
-      <c r="B38" s="112"/>
-      <c r="C38" s="112"/>
-      <c r="D38" s="112"/>
-      <c r="E38" s="112"/>
-      <c r="F38" s="112"/>
-      <c r="G38" s="112"/>
+      <c r="B38" s="113"/>
+      <c r="C38" s="113"/>
+      <c r="D38" s="113"/>
+      <c r="E38" s="113"/>
+      <c r="F38" s="113"/>
+      <c r="G38" s="113"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" s="112" t="s">
+      <c r="A39" s="113" t="s">
         <v>181</v>
       </c>
-      <c r="B39" s="112"/>
-      <c r="C39" s="112"/>
-      <c r="D39" s="112"/>
-      <c r="E39" s="112"/>
-      <c r="F39" s="112"/>
-      <c r="G39" s="112"/>
+      <c r="B39" s="113"/>
+      <c r="C39" s="113"/>
+      <c r="D39" s="113"/>
+      <c r="E39" s="113"/>
+      <c r="F39" s="113"/>
+      <c r="G39" s="113"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" s="112" t="s">
+      <c r="A40" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="B40" s="112"/>
-      <c r="C40" s="112"/>
-      <c r="D40" s="112"/>
-      <c r="E40" s="112"/>
-      <c r="F40" s="112"/>
-      <c r="G40" s="112"/>
+      <c r="B40" s="113"/>
+      <c r="C40" s="113"/>
+      <c r="D40" s="113"/>
+      <c r="E40" s="113"/>
+      <c r="F40" s="113"/>
+      <c r="G40" s="113"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" s="112" t="s">
+      <c r="A41" s="113" t="s">
         <v>183</v>
       </c>
-      <c r="B41" s="112"/>
-      <c r="C41" s="112"/>
-      <c r="D41" s="112"/>
-      <c r="E41" s="112"/>
-      <c r="F41" s="112"/>
-      <c r="G41" s="112"/>
+      <c r="B41" s="113"/>
+      <c r="C41" s="113"/>
+      <c r="D41" s="113"/>
+      <c r="E41" s="113"/>
+      <c r="F41" s="113"/>
+      <c r="G41" s="113"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="53" t="s">
@@ -5092,50 +5101,50 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="112" t="s">
+      <c r="A44" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="B44" s="112"/>
-      <c r="C44" s="112"/>
-      <c r="D44" s="112"/>
-      <c r="E44" s="112"/>
-      <c r="F44" s="112"/>
-      <c r="G44" s="112"/>
+      <c r="B44" s="113"/>
+      <c r="C44" s="113"/>
+      <c r="D44" s="113"/>
+      <c r="E44" s="113"/>
+      <c r="F44" s="113"/>
+      <c r="G44" s="113"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="112" t="s">
+      <c r="A45" s="113" t="s">
         <v>186</v>
       </c>
-      <c r="B45" s="112"/>
-      <c r="C45" s="112"/>
-      <c r="D45" s="112"/>
-      <c r="E45" s="112"/>
-      <c r="F45" s="112"/>
-      <c r="G45" s="112"/>
+      <c r="B45" s="113"/>
+      <c r="C45" s="113"/>
+      <c r="D45" s="113"/>
+      <c r="E45" s="113"/>
+      <c r="F45" s="113"/>
+      <c r="G45" s="113"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="112" t="s">
+      <c r="A46" s="113" t="s">
         <v>187</v>
       </c>
-      <c r="B46" s="112"/>
-      <c r="C46" s="112"/>
-      <c r="D46" s="112"/>
-      <c r="E46" s="112"/>
-      <c r="F46" s="112"/>
-      <c r="G46" s="112"/>
+      <c r="B46" s="113"/>
+      <c r="C46" s="113"/>
+      <c r="D46" s="113"/>
+      <c r="E46" s="113"/>
+      <c r="F46" s="113"/>
+      <c r="G46" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A46:G46"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A37:G37"/>
     <mergeCell ref="A38:G38"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -5165,14 +5174,14 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="115" t="s">
+      <c r="A2" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
       <c r="G2" s="55">
         <v>1</v>
       </c>
@@ -5195,6 +5204,11 @@
         <f>Выбросы!C8</f>
         <v>135.30000000000001</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E4" s="59" t="s">
         <v>192</v>
       </c>
@@ -5210,6 +5224,11 @@
         <f>C6</f>
         <v>0.02</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -5219,6 +5238,11 @@
       <c r="C6" s="4">
         <v>0.02</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E6" s="59" t="s">
         <v>196</v>
       </c>
@@ -5234,6 +5258,11 @@
         <f>MACC!$E$45</f>
         <v>500</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E7" s="59" t="s">
         <v>72</v>
       </c>
@@ -5248,6 +5277,11 @@
       <c r="C8" s="62">
         <v>0.55000000000000004</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F8" s="5" t="s">
         <v>201</v>
       </c>
@@ -5260,6 +5294,11 @@
         <f>MACC!$E$36</f>
         <v>15</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E9" s="59" t="s">
         <v>53</v>
       </c>
@@ -5275,6 +5314,11 @@
         <f>MACC!$E$42</f>
         <v>0.4</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="F10" s="5" t="s">
         <v>202</v>
       </c>
@@ -5285,6 +5329,11 @@
       </c>
       <c r="C11" s="64">
         <v>20</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E11" s="59" t="s">
         <v>204</v>
@@ -5308,6 +5357,11 @@
         <f>C4*C5*1000</f>
         <v>2706.0000000000005</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E13" s="59" t="s">
         <v>207</v>
       </c>
@@ -5318,6 +5372,11 @@
       </c>
       <c r="C14" s="66">
         <v>15000</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E14" s="59" t="s">
         <v>209</v>
@@ -5344,6 +5403,11 @@
         <f>C14*C7/1000</f>
         <v>7500</v>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="17" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B17" s="3" t="s">
@@ -5352,6 +5416,11 @@
       <c r="C17" s="67">
         <f>C16*0.3</f>
         <v>2250</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="F17" s="5" t="s">
         <v>214</v>
@@ -5388,6 +5457,11 @@
         <f>C18*E20</f>
         <v>97.5</v>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E20" s="71">
         <v>0.01</v>
       </c>
@@ -5402,6 +5476,11 @@
       <c r="C21" s="67">
         <f>E21*C9</f>
         <v>-27.675000000000004</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E21" s="72">
         <f>-C13*1000/(C10*44/12)/10^6</f>
@@ -5442,6 +5521,11 @@
         <f>C18</f>
         <v>9750</v>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E24" s="59" t="s">
         <v>224</v>
       </c>
@@ -5454,6 +5538,11 @@
         <f>C22</f>
         <v>69.824999999999989</v>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E25" s="59" t="s">
         <v>226</v>
       </c>
@@ -5466,6 +5555,11 @@
         <f>C11</f>
         <v>20</v>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E26" s="59" t="s">
         <v>204</v>
       </c>
@@ -5478,20 +5572,25 @@
         <f>C13</f>
         <v>2706.0000000000005</v>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E27" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="115" t="s">
+      <c r="A29" s="114" t="s">
         <v>227</v>
       </c>
-      <c r="B29" s="115"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="115"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
+      <c r="B29" s="114"/>
+      <c r="C29" s="114"/>
+      <c r="D29" s="114"/>
+      <c r="E29" s="114"/>
+      <c r="F29" s="114"/>
       <c r="G29" s="55">
         <v>1</v>
       </c>
@@ -5514,6 +5613,11 @@
         <f>Выбросы!C8</f>
         <v>135.30000000000001</v>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E31" s="59" t="s">
         <v>192</v>
       </c>
@@ -5529,6 +5633,11 @@
         <f>C42/1000/C31</f>
         <v>8.9024390243902449E-2</v>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F32" s="5" t="s">
         <v>228</v>
       </c>
@@ -5541,6 +5650,11 @@
         <f>MACC!$E$46</f>
         <v>1500</v>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E33" s="59" t="s">
         <v>72</v>
       </c>
@@ -5555,6 +5669,11 @@
       <c r="C34" s="4">
         <v>0.4</v>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F34" s="5" t="s">
         <v>232</v>
       </c>
@@ -5567,6 +5686,11 @@
         <f>MACC!$E$37</f>
         <v>250</v>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E35" s="59" t="s">
         <v>56</v>
       </c>
@@ -5582,6 +5706,11 @@
         <f>MACC!$E$36</f>
         <v>15</v>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E36" s="59" t="s">
         <v>53</v>
       </c>
@@ -5597,6 +5726,11 @@
         <f>MACC!$E$39</f>
         <v>1</v>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E37" s="59" t="s">
         <v>236</v>
       </c>
@@ -5610,6 +5744,11 @@
         <f>MACC!$E$40</f>
         <v>0.45</v>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E38" s="59" t="s">
         <v>236</v>
       </c>
@@ -5622,6 +5761,11 @@
       <c r="C39" s="62">
         <v>0.5</v>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
     </row>
     <row r="40" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B40" s="3" t="s">
@@ -5629,6 +5773,11 @@
       </c>
       <c r="C40" s="64">
         <v>20</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E40" s="59" t="s">
         <v>204</v>
@@ -5652,6 +5801,11 @@
         <f>C43*8760*C39*(C37-C38)*10^-3</f>
         <v>12045.000000000002</v>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E42" s="59" t="s">
         <v>207</v>
       </c>
@@ -5662,6 +5816,11 @@
       </c>
       <c r="C43" s="79">
         <v>5000</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E43" s="59" t="s">
         <v>209</v>
@@ -5685,6 +5844,11 @@
         <f>C43*C33/1000</f>
         <v>7500</v>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="46" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B46" s="3" t="s">
@@ -5693,6 +5857,11 @@
       <c r="C46" s="67">
         <f>C45*C34</f>
         <v>3000</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -5726,6 +5895,11 @@
         <f>C43*E49*12*10^-3</f>
         <v>-120</v>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E49" s="59">
         <v>-2</v>
       </c>
@@ -5741,6 +5915,11 @@
         <f>E50*10^-3*C35</f>
         <v>1171.30195599022</v>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E50" s="72">
         <f>C43*8760*C39*250*7000/8180*10^-6</f>
         <v>4685.20782396088</v>
@@ -5756,6 +5935,11 @@
       <c r="C51" s="67">
         <f>E51*C36</f>
         <v>-123.1875</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E51" s="72">
         <f>-C42*1000/(C10*44/12)/10^6</f>
@@ -5796,6 +5980,11 @@
         <f>C47</f>
         <v>10500</v>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E54" s="59" t="s">
         <v>224</v>
       </c>
@@ -5808,6 +5997,11 @@
         <f>C52</f>
         <v>928.11445599021999</v>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E55" s="59" t="s">
         <v>226</v>
       </c>
@@ -5820,6 +6014,11 @@
         <f>C40</f>
         <v>20</v>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E56" s="59" t="s">
         <v>204</v>
       </c>
@@ -5832,20 +6031,25 @@
         <f>C42</f>
         <v>12045.000000000002</v>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E57" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="58" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="59" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="115" t="s">
+      <c r="A59" s="114" t="s">
         <v>245</v>
       </c>
-      <c r="B59" s="115"/>
-      <c r="C59" s="115"/>
-      <c r="D59" s="115"/>
-      <c r="E59" s="115"/>
-      <c r="F59" s="115"/>
+      <c r="B59" s="114"/>
+      <c r="C59" s="114"/>
+      <c r="D59" s="114"/>
+      <c r="E59" s="114"/>
+      <c r="F59" s="114"/>
       <c r="G59" s="55">
         <v>1</v>
       </c>
@@ -5868,6 +6072,11 @@
         <f>Выбросы!C8</f>
         <v>135.30000000000001</v>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E61" s="59" t="s">
         <v>192</v>
       </c>
@@ -5882,6 +6091,11 @@
       <c r="C62" s="4">
         <v>0.2</v>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F62" s="5" t="s">
         <v>228</v>
       </c>
@@ -5894,6 +6108,11 @@
         <f>0.4*(1-C67)+0.2*C67</f>
         <v>0.35000000000000003</v>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F63" s="5" t="s">
         <v>247</v>
       </c>
@@ -5905,6 +6124,11 @@
       <c r="C64" s="62">
         <v>0.1</v>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F64" s="5"/>
     </row>
     <row r="65" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -5915,6 +6139,11 @@
         <f>MACC!$E$47</f>
         <v>500</v>
       </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E65" s="59" t="s">
         <v>72</v>
       </c>
@@ -5930,6 +6159,11 @@
         <f>MACC!$E$48</f>
         <v>900</v>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E66" s="59" t="s">
         <v>72</v>
       </c>
@@ -5944,6 +6178,11 @@
       <c r="C67" s="4">
         <v>0.25</v>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F67" s="5" t="s">
         <v>253</v>
       </c>
@@ -5955,6 +6194,11 @@
       <c r="C68" s="4">
         <v>0.15</v>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E68" s="59" t="s">
         <v>255</v>
       </c>
@@ -5970,6 +6214,11 @@
         <f>MACC!$E$36</f>
         <v>15</v>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E69" s="59" t="s">
         <v>53</v>
       </c>
@@ -5985,6 +6234,11 @@
         <f>MACC!$E$42</f>
         <v>0.4</v>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="F70" s="5" t="s">
         <v>257</v>
       </c>
@@ -5995,6 +6249,11 @@
       </c>
       <c r="C71" s="64">
         <v>25</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E71" s="59" t="s">
         <v>204</v>
@@ -6018,6 +6277,11 @@
         <f>C74*8760*C63*(1-C64)*C37*10^-3</f>
         <v>27594.000000000004</v>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E73" s="59" t="s">
         <v>207</v>
       </c>
@@ -6028,6 +6292,11 @@
       </c>
       <c r="C74" s="65">
         <v>10000</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E74" s="59" t="s">
         <v>209</v>
@@ -6054,6 +6323,11 @@
         <f>(C66*(1-C67)+C65*C67)*C74*10^-3</f>
         <v>8000</v>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="77" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B77" s="3" t="s">
@@ -6062,6 +6336,11 @@
       <c r="C77" s="67">
         <f>C76*C68</f>
         <v>1200</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -6095,6 +6374,11 @@
         <f>C78*0.015</f>
         <v>138</v>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F80" s="5" t="s">
         <v>263</v>
       </c>
@@ -6106,6 +6390,11 @@
       <c r="C81" s="67">
         <f>-C73*1000/(C70*44/12)*C69/10^6</f>
         <v>-282.21136363636361</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="F81" s="5" t="s">
         <v>264</v>
@@ -6145,6 +6434,11 @@
         <f>C78</f>
         <v>9200</v>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E85" s="59" t="s">
         <v>224</v>
       </c>
@@ -6157,6 +6451,11 @@
         <f>C82</f>
         <v>-144.21136363636361</v>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E86" s="59" t="s">
         <v>226</v>
       </c>
@@ -6169,6 +6468,11 @@
         <f>C71</f>
         <v>25</v>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E87" s="59" t="s">
         <v>204</v>
       </c>
@@ -6181,20 +6485,25 @@
         <f>C73</f>
         <v>27594.000000000004</v>
       </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E88" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="89" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="90" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="115" t="s">
+      <c r="A90" s="114" t="s">
         <v>265</v>
       </c>
-      <c r="B90" s="115"/>
-      <c r="C90" s="115"/>
-      <c r="D90" s="115"/>
-      <c r="E90" s="115"/>
-      <c r="F90" s="115"/>
+      <c r="B90" s="114"/>
+      <c r="C90" s="114"/>
+      <c r="D90" s="114"/>
+      <c r="E90" s="114"/>
+      <c r="F90" s="114"/>
       <c r="G90" s="55">
         <v>1</v>
       </c>
@@ -6217,6 +6526,11 @@
         <f>Выбросы!C8</f>
         <v>135.30000000000001</v>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E92" s="59" t="s">
         <v>192</v>
       </c>
@@ -6232,6 +6546,11 @@
         <f>C112/C92/1000</f>
         <v>2.9782705099778265E-2</v>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F93" s="5" t="s">
         <v>228</v>
       </c>
@@ -6244,6 +6563,11 @@
         <f>C139</f>
         <v>0.35000000000000003</v>
       </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F94" s="5" t="s">
         <v>267</v>
       </c>
@@ -6256,6 +6580,11 @@
         <f>C140</f>
         <v>800</v>
       </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E95" s="59" t="s">
         <v>72</v>
       </c>
@@ -6270,6 +6599,11 @@
       <c r="C96" s="66">
         <v>3000</v>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E96" s="59" t="s">
         <v>72</v>
       </c>
@@ -6283,6 +6617,11 @@
         <f>MACC!$E$49</f>
         <v>1000</v>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E97" s="59" t="s">
         <v>72</v>
       </c>
@@ -6297,6 +6636,11 @@
       <c r="C98" s="81">
         <v>0.47</v>
       </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E98" s="59"/>
       <c r="F98" s="5"/>
     </row>
@@ -6307,6 +6651,11 @@
       <c r="C99" s="66">
         <v>200</v>
       </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E99" s="59" t="s">
         <v>88</v>
       </c>
@@ -6322,6 +6671,11 @@
         <f>H115*10^3/8760/C103</f>
         <v>400</v>
       </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F100" s="5"/>
     </row>
     <row r="101" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -6331,6 +6685,11 @@
       <c r="C101" s="4">
         <v>0.55000000000000004</v>
       </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F101" s="5"/>
     </row>
     <row r="102" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -6340,6 +6699,11 @@
       <c r="C102" s="4">
         <v>0.2</v>
       </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F102" s="5"/>
     </row>
     <row r="103" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -6349,6 +6713,11 @@
       <c r="C103" s="4">
         <v>0.3</v>
       </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F103" s="5"/>
     </row>
     <row r="104" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -6358,6 +6727,11 @@
       <c r="C104" s="4">
         <v>0.4</v>
       </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F104" s="5" t="s">
         <v>280</v>
       </c>
@@ -6369,6 +6743,11 @@
       <c r="C105" s="4">
         <v>0.15</v>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F105" s="5" t="s">
         <v>282</v>
       </c>
@@ -6381,6 +6760,11 @@
         <f>MACC!$E$36</f>
         <v>15</v>
       </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E106" s="59" t="s">
         <v>53</v>
       </c>
@@ -6393,6 +6777,11 @@
         <f>MACC!$E$37</f>
         <v>250</v>
       </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E107" s="59" t="s">
         <v>283</v>
       </c>
@@ -6405,6 +6794,11 @@
         <f>MACC!$E$42</f>
         <v>0.4</v>
       </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
     </row>
     <row r="109" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B109" s="3" t="s">
@@ -6413,6 +6807,11 @@
       <c r="C109" s="64">
         <v>25</v>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E109" s="59" t="s">
         <v>204</v>
       </c>
@@ -6424,6 +6823,11 @@
       <c r="C110" s="82">
         <f>G115-G114+H115</f>
         <v>4117.2</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E110" s="59"/>
     </row>
@@ -6445,6 +6849,11 @@
         <f>$G$115*$C$37-$G$114*$C$38</f>
         <v>4029.6</v>
       </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E112" s="59" t="s">
         <v>207</v>
       </c>
@@ -6460,6 +6869,11 @@
         <f>C110/8760/C94*10^3</f>
         <v>1342.8571428571427</v>
       </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E113" s="59" t="s">
         <v>209</v>
       </c>
@@ -6478,6 +6892,11 @@
         <f>C115</f>
         <v>1000</v>
       </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E114" s="59" t="s">
         <v>209</v>
       </c>
@@ -6492,6 +6911,11 @@
       </c>
       <c r="C115" s="79">
         <v>1000</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E115" s="59" t="s">
         <v>209</v>
@@ -6523,6 +6947,11 @@
         <f>C113*C95/1000</f>
         <v>1074.285714285714</v>
       </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="118" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B118" s="3" t="s">
@@ -6532,6 +6961,11 @@
         <f>C105*C120</f>
         <v>150</v>
       </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F118" s="5" t="s">
         <v>293</v>
       </c>
@@ -6544,6 +6978,11 @@
         <f>-C114*C96/1000</f>
         <v>-3000</v>
       </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="120" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B120" s="3" t="s">
@@ -6553,6 +6992,11 @@
         <f>C114*C97/1000</f>
         <v>1000</v>
       </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="121" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B121" s="3" t="s">
@@ -6561,6 +7005,11 @@
       <c r="C121" s="67">
         <f>C100*C99/1000</f>
         <v>80</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="F121" s="5" t="s">
         <v>297</v>
@@ -6597,6 +7046,11 @@
         <f>C122*0.015</f>
         <v>-10.43571428571429</v>
       </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="125" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B125" s="3" t="s">
@@ -6606,6 +7060,11 @@
         <f>C115*E125*12*10^-3*0</f>
         <v>0</v>
       </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E125" s="72">
         <v>-2</v>
       </c>
@@ -6621,6 +7080,11 @@
         <f>E126*C107*10^-3</f>
         <v>98.090308484627798</v>
       </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E126" s="72">
         <f>G114*10^3*(123/C98)*10^-6*7000/8180</f>
         <v>392.36123393851119</v>
@@ -6636,6 +7100,11 @@
       <c r="C127" s="67">
         <f>E127*C106</f>
         <v>-10.987012987012983</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E127" s="72">
         <f>-C117*1000/(C108*44/12)/10^6</f>
@@ -6676,6 +7145,11 @@
         <f>C122</f>
         <v>-695.71428571428601</v>
       </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E130" s="59" t="s">
         <v>224</v>
       </c>
@@ -6688,6 +7162,11 @@
         <f>C128</f>
         <v>76.667581211900526</v>
       </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E131" s="59" t="s">
         <v>226</v>
       </c>
@@ -6700,6 +7179,11 @@
         <f>C109</f>
         <v>25</v>
       </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E132" s="59" t="s">
         <v>204</v>
       </c>
@@ -6712,20 +7196,25 @@
         <f>C112</f>
         <v>4029.6</v>
       </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E133" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="134" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="135" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="115" t="s">
+      <c r="A135" s="114" t="s">
         <v>301</v>
       </c>
-      <c r="B135" s="115"/>
-      <c r="C135" s="115"/>
-      <c r="D135" s="115"/>
-      <c r="E135" s="115"/>
-      <c r="F135" s="115"/>
+      <c r="B135" s="114"/>
+      <c r="C135" s="114"/>
+      <c r="D135" s="114"/>
+      <c r="E135" s="114"/>
+      <c r="F135" s="114"/>
       <c r="G135" s="55">
         <v>1</v>
       </c>
@@ -6748,6 +7237,11 @@
         <f>Выбросы!C8</f>
         <v>135.30000000000001</v>
       </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E137" s="59" t="s">
         <v>192</v>
       </c>
@@ -6763,6 +7257,11 @@
         <f>C155/C137/1000</f>
         <v>0.20847893569844789</v>
       </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F138" s="5" t="s">
         <v>228</v>
       </c>
@@ -6775,6 +7274,11 @@
         <f>C63</f>
         <v>0.35000000000000003</v>
       </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F139" s="5" t="s">
         <v>267</v>
       </c>
@@ -6788,6 +7292,11 @@
         <f>(C66*(1-C67)+C65*C67)</f>
         <v>800</v>
       </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E140" s="59" t="s">
         <v>72</v>
       </c>
@@ -6802,6 +7311,11 @@
       <c r="C141" s="66">
         <v>1000</v>
       </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E141" s="59" t="s">
         <v>72</v>
       </c>
@@ -6815,6 +7329,11 @@
         <f>MACC!$E$49</f>
         <v>1000</v>
       </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E142" s="59" t="s">
         <v>72</v>
       </c>
@@ -6829,6 +7348,11 @@
       <c r="C143" s="66">
         <v>100</v>
       </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E143" s="59" t="s">
         <v>88</v>
       </c>
@@ -6844,6 +7368,11 @@
         <f>H158*10^3/8760/C147</f>
         <v>2800.0000000000005</v>
       </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F144" s="5"/>
     </row>
     <row r="145" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -6853,6 +7382,11 @@
       <c r="C145" s="4">
         <v>0.55000000000000004</v>
       </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F145" s="5"/>
     </row>
     <row r="146" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -6862,6 +7396,11 @@
       <c r="C146" s="4">
         <v>0.2</v>
       </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F146" s="5"/>
     </row>
     <row r="147" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -6871,6 +7410,11 @@
       <c r="C147" s="4">
         <v>0.3</v>
       </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F147" s="5"/>
     </row>
     <row r="148" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -6880,6 +7424,11 @@
       <c r="C148" s="4">
         <v>0.4</v>
       </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F148" s="5"/>
     </row>
     <row r="149" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -6890,6 +7439,11 @@
         <f>MACC!$E$36</f>
         <v>15</v>
       </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E149" s="59" t="s">
         <v>53</v>
       </c>
@@ -6902,6 +7456,11 @@
         <f>MACC!$E$37</f>
         <v>250</v>
       </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E150" s="59" t="s">
         <v>283</v>
       </c>
@@ -6914,6 +7473,11 @@
         <f>MACC!$E$42</f>
         <v>0.4</v>
       </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
     </row>
     <row r="152" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B152" s="3" t="s">
@@ -6922,6 +7486,11 @@
       <c r="C152" s="64">
         <v>25</v>
       </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E152" s="59" t="s">
         <v>204</v>
       </c>
@@ -6933,6 +7502,11 @@
       <c r="C153" s="82">
         <f>G156</f>
         <v>21462</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E153" s="59"/>
     </row>
@@ -6954,6 +7528,11 @@
         <f>$G$158*$C$37-$G$157*$C$38</f>
         <v>28207.200000000001</v>
       </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E155" s="59" t="s">
         <v>207</v>
       </c>
@@ -6972,6 +7551,11 @@
         <f>C153/8760/C139*10^3</f>
         <v>7000</v>
       </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E156" s="59" t="s">
         <v>209</v>
       </c>
@@ -6988,6 +7572,11 @@
         <f>C158</f>
         <v>7000</v>
       </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E157" s="59" t="s">
         <v>209</v>
       </c>
@@ -7002,6 +7591,11 @@
       </c>
       <c r="C158" s="79">
         <v>7000</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E158" s="59" t="s">
         <v>209</v>
@@ -7033,6 +7627,11 @@
         <f>C156*C140/1000</f>
         <v>5600</v>
       </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="161" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B161" s="3" t="s">
@@ -7042,6 +7641,11 @@
         <f>C157*C142/1000</f>
         <v>7000</v>
       </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="162" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B162" s="3" t="s">
@@ -7051,6 +7655,11 @@
         <f>-C141*C158*10^-3</f>
         <v>-7000</v>
       </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="163" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B163" s="3" t="s">
@@ -7059,6 +7668,11 @@
       <c r="C163" s="67">
         <f>C144*C143/1000</f>
         <v>280.00000000000006</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="F163" s="5" t="s">
         <v>297</v>
@@ -7095,6 +7709,11 @@
         <f>C164*0.015</f>
         <v>88.2</v>
       </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="167" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B167" s="3" t="s">
@@ -7104,6 +7723,11 @@
         <f>C158*E167*12*10^-3</f>
         <v>-168</v>
       </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E167" s="72">
         <v>-2</v>
       </c>
@@ -7119,6 +7743,11 @@
         <f>E168*C150*10^-3</f>
         <v>918.30073349633244</v>
       </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E168" s="72">
         <f>G157*10^3*350*10^-6*7000/8180</f>
         <v>3673.2029339853298</v>
@@ -7134,6 +7763,11 @@
       <c r="C169" s="67">
         <f>E169*C149</f>
         <v>-57.272727272727266</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E169" s="72">
         <f>-C160*1000/(C151*44/12)/10^6</f>
@@ -7174,6 +7808,11 @@
         <f>C164</f>
         <v>5880</v>
       </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E172" s="59" t="s">
         <v>224</v>
       </c>
@@ -7186,6 +7825,11 @@
         <f>C170</f>
         <v>781.22800622360523</v>
       </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E173" s="59" t="s">
         <v>226</v>
       </c>
@@ -7198,6 +7842,11 @@
         <f>C152</f>
         <v>25</v>
       </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E174" s="59" t="s">
         <v>204</v>
       </c>
@@ -7210,20 +7859,25 @@
         <f>C155</f>
         <v>28207.200000000001</v>
       </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E175" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="176" spans="1:6" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="177" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A177" s="115" t="s">
+      <c r="A177" s="114" t="s">
         <v>312</v>
       </c>
-      <c r="B177" s="115"/>
-      <c r="C177" s="115"/>
-      <c r="D177" s="115"/>
-      <c r="E177" s="115"/>
-      <c r="F177" s="115"/>
+      <c r="B177" s="114"/>
+      <c r="C177" s="114"/>
+      <c r="D177" s="114"/>
+      <c r="E177" s="114"/>
+      <c r="F177" s="114"/>
       <c r="G177" s="55">
         <v>1</v>
       </c>
@@ -7246,6 +7900,11 @@
         <f>Выбросы!C8</f>
         <v>135.30000000000001</v>
       </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E179" s="59" t="s">
         <v>192</v>
       </c>
@@ -7261,6 +7920,11 @@
         <f>C190/C179/1000</f>
         <v>0.19811973392461199</v>
       </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F180" s="5" t="s">
         <v>228</v>
       </c>
@@ -7273,6 +7937,11 @@
         <f>MACC!$E$50</f>
         <v>7700</v>
       </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E181" s="59" t="s">
         <v>72</v>
       </c>
@@ -7287,6 +7956,11 @@
       <c r="C182" s="84">
         <v>1.3</v>
       </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E182" s="59"/>
       <c r="F182" s="5"/>
     </row>
@@ -7297,6 +7971,11 @@
       <c r="C183" s="62">
         <v>0.85</v>
       </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F183" s="5" t="s">
         <v>316</v>
       </c>
@@ -7308,6 +7987,11 @@
       <c r="C184" s="66">
         <v>15</v>
       </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E184" s="59" t="s">
         <v>59</v>
       </c>
@@ -7322,6 +8006,11 @@
       <c r="C185" s="66">
         <v>5</v>
       </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E185" s="59" t="s">
         <v>59</v>
       </c>
@@ -7337,6 +8026,11 @@
         <f>MACC!$E$36</f>
         <v>15</v>
       </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E186" s="59" t="s">
         <v>53</v>
       </c>
@@ -7349,6 +8043,11 @@
         <f>MACC!$E$42</f>
         <v>0.4</v>
       </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
     </row>
     <row r="188" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B188" s="3" t="s">
@@ -7356,6 +8055,11 @@
       </c>
       <c r="C188" s="64">
         <v>60</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E188" s="59" t="s">
         <v>204</v>
@@ -7379,6 +8083,11 @@
         <f>G191*C37*10^-3</f>
         <v>26805.600000000002</v>
       </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E190" s="59" t="s">
         <v>207</v>
       </c>
@@ -7390,6 +8099,11 @@
       <c r="C191" s="65">
         <v>3600</v>
       </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E191" s="59" t="s">
         <v>209</v>
       </c>
@@ -7405,6 +8119,11 @@
       <c r="C192" s="65">
         <f>C191*8760*C183/1000</f>
         <v>26805.599999999999</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E192" s="59" t="s">
         <v>322</v>
@@ -7428,6 +8147,11 @@
         <f>C191*C181/1000*C182</f>
         <v>36036</v>
       </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="195" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A195" s="68"/>
@@ -7460,6 +8184,11 @@
         <f>C192*C184/1000</f>
         <v>402.084</v>
       </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="198" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B198" s="3" t="s">
@@ -7469,6 +8198,11 @@
         <f>C192*C185/1000</f>
         <v>134.02799999999999</v>
       </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="199" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B199" s="3" t="s">
@@ -7477,6 +8211,11 @@
       <c r="C199" s="67">
         <f>E199*C186</f>
         <v>-274.14818181818185</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E199" s="72">
         <f>-C190*1000/(C187*44/12)/10^6</f>
@@ -7517,6 +8256,11 @@
         <f>C195</f>
         <v>36036</v>
       </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E202" s="59" t="s">
         <v>224</v>
       </c>
@@ -7529,6 +8273,11 @@
         <f>C200</f>
         <v>261.96381818181811</v>
       </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E203" s="59" t="s">
         <v>226</v>
       </c>
@@ -7541,6 +8290,11 @@
         <f>C188</f>
         <v>60</v>
       </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E204" s="59" t="s">
         <v>204</v>
       </c>
@@ -7553,20 +8307,25 @@
         <f>C190</f>
         <v>26805.600000000002</v>
       </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E205" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="206" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="207" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A207" s="115" t="s">
+      <c r="A207" s="114" t="s">
         <v>326</v>
       </c>
-      <c r="B207" s="115"/>
-      <c r="C207" s="115"/>
-      <c r="D207" s="115"/>
-      <c r="E207" s="115"/>
-      <c r="F207" s="115"/>
+      <c r="B207" s="114"/>
+      <c r="C207" s="114"/>
+      <c r="D207" s="114"/>
+      <c r="E207" s="114"/>
+      <c r="F207" s="114"/>
       <c r="G207" s="55">
         <v>1</v>
       </c>
@@ -7589,6 +8348,11 @@
         <f>Выбросы!C8</f>
         <v>135.30000000000001</v>
       </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E209" s="59" t="s">
         <v>192</v>
       </c>
@@ -7604,6 +8368,11 @@
         <f>C225/C209/1000</f>
         <v>3.8617886178861791E-2</v>
       </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F210" s="5"/>
     </row>
     <row r="211" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -7613,6 +8382,11 @@
       <c r="C211" s="66">
         <v>95000</v>
       </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E211" s="1" t="s">
         <v>328</v>
       </c>
@@ -7627,6 +8401,11 @@
         <f>G212*C211</f>
         <v>9500</v>
       </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E212" s="1" t="s">
         <v>328</v>
       </c>
@@ -7644,6 +8423,11 @@
       <c r="C213" s="87">
         <v>3.5</v>
       </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F213" s="5" t="s">
         <v>332</v>
       </c>
@@ -7656,6 +8440,11 @@
         <f>MACC!$E$51</f>
         <v>1750</v>
       </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E214" s="59" t="s">
         <v>83</v>
       </c>
@@ -7670,6 +8459,11 @@
       <c r="C215" s="4">
         <v>0.3</v>
       </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E215" s="59" t="s">
         <v>336</v>
       </c>
@@ -7683,6 +8477,11 @@
         <f>MACC!$E$38</f>
         <v>50</v>
       </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E216" s="59" t="s">
         <v>59</v>
       </c>
@@ -7697,6 +8496,11 @@
       <c r="C217" s="66">
         <v>180</v>
       </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E217" s="59" t="s">
         <v>340</v>
       </c>
@@ -7709,6 +8513,11 @@
         <f>MACC!$E$41</f>
         <v>0.55000000000000004</v>
       </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E218" s="59" t="s">
         <v>341</v>
       </c>
@@ -7722,6 +8531,11 @@
         <f>MACC!$E$42</f>
         <v>0.4</v>
       </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E219" s="59"/>
       <c r="F219" s="5"/>
     </row>
@@ -7732,6 +8546,11 @@
       <c r="C220" s="62">
         <v>0.3</v>
       </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F220" s="5" t="s">
         <v>343</v>
       </c>
@@ -7743,6 +8562,11 @@
       <c r="C221" s="62">
         <v>0.1</v>
       </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F221" s="5"/>
     </row>
     <row r="222" spans="1:8" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -7753,6 +8577,11 @@
         <f>MACC!$E$36</f>
         <v>15</v>
       </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E222" s="59" t="s">
         <v>53</v>
       </c>
@@ -7766,6 +8595,11 @@
       </c>
       <c r="C223" s="64">
         <v>20</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E223" s="59" t="s">
         <v>204</v>
@@ -7789,6 +8623,11 @@
         <f>C212*C218</f>
         <v>5225</v>
       </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E225" s="59" t="s">
         <v>207</v>
       </c>
@@ -7801,6 +8640,11 @@
         <f>C225*1000*1.163/(8760*C220)*(1-C221)</f>
         <v>2081.053082191781</v>
       </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E226" s="59" t="s">
         <v>346</v>
       </c>
@@ -7813,6 +8657,11 @@
         <f>C226/C213</f>
         <v>594.58659491193737</v>
       </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E227" s="59" t="s">
         <v>348</v>
       </c>
@@ -7824,6 +8673,11 @@
       <c r="C228" s="65">
         <f>C227*8760*C220/1000</f>
         <v>1562.5735714285711</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E228" s="59" t="s">
         <v>350</v>
@@ -7847,6 +8701,11 @@
         <f>C227*C214/1000</f>
         <v>1040.5265410958903</v>
       </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="231" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B231" s="3" t="s">
@@ -7855,6 +8714,11 @@
       <c r="C231" s="67">
         <f>C230*C215</f>
         <v>312.15796232876704</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="232" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -7888,6 +8752,11 @@
         <f>C232*E234</f>
         <v>27.053690068493147</v>
       </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E234" s="88">
         <v>0.02</v>
       </c>
@@ -7900,6 +8769,11 @@
         <f>-C234</f>
         <v>-27.053690068493147</v>
       </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E235" s="88"/>
       <c r="F235" s="5" t="s">
         <v>353</v>
@@ -7913,6 +8787,11 @@
         <f>C228*C216/1000</f>
         <v>78.128678571428551</v>
       </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="237" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B237" s="3" t="s">
@@ -7921,6 +8800,11 @@
       <c r="C237" s="67">
         <f>E237*C222</f>
         <v>-53.437499999999993</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E237" s="72">
         <f>-C225*1000/(C219*44/12)/10^6</f>
@@ -7961,6 +8845,11 @@
         <f>C232</f>
         <v>1352.6845034246574</v>
       </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E240" s="59" t="s">
         <v>224</v>
       </c>
@@ -7973,6 +8862,11 @@
         <f>C238</f>
         <v>24.691178571428559</v>
       </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E241" s="59" t="s">
         <v>226</v>
       </c>
@@ -7985,6 +8879,11 @@
         <f>C223</f>
         <v>20</v>
       </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E242" s="59" t="s">
         <v>204</v>
       </c>
@@ -7997,20 +8896,25 @@
         <f>C225</f>
         <v>5225</v>
       </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E243" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="244" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="245" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A245" s="115" t="s">
+      <c r="A245" s="114" t="s">
         <v>355</v>
       </c>
-      <c r="B245" s="115"/>
-      <c r="C245" s="115"/>
-      <c r="D245" s="115"/>
-      <c r="E245" s="115"/>
-      <c r="F245" s="115"/>
+      <c r="B245" s="114"/>
+      <c r="C245" s="114"/>
+      <c r="D245" s="114"/>
+      <c r="E245" s="114"/>
+      <c r="F245" s="114"/>
       <c r="G245" s="55">
         <v>1</v>
       </c>
@@ -8033,6 +8937,11 @@
         <f>Выбросы!C8</f>
         <v>135.30000000000001</v>
       </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E247" s="59" t="s">
         <v>192</v>
       </c>
@@ -8047,6 +8956,11 @@
       <c r="C248" s="66">
         <v>95000</v>
       </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E248" s="1" t="s">
         <v>328</v>
       </c>
@@ -8060,6 +8974,11 @@
         <f>C248*1.163/8760/C255*10^3</f>
         <v>42041.476407914764</v>
       </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E249" s="1" t="s">
         <v>209</v>
       </c>
@@ -8073,6 +8992,11 @@
         <f>C263/C247/1000</f>
         <v>0.20853658536585368</v>
       </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F250" s="5"/>
     </row>
     <row r="251" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -8083,6 +9007,11 @@
         <f>MACC!$E$52</f>
         <v>150</v>
       </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E251" s="59" t="s">
         <v>72</v>
       </c>
@@ -8097,6 +9026,11 @@
       <c r="C252" s="4">
         <v>0.4</v>
       </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E252" s="59" t="s">
         <v>359</v>
       </c>
@@ -8108,6 +9042,11 @@
       <c r="C253" s="66">
         <v>180</v>
       </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E253" s="59" t="s">
         <v>340</v>
       </c>
@@ -8120,6 +9059,11 @@
         <f>MACC!$E$41</f>
         <v>0.55000000000000004</v>
       </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E254" s="59" t="s">
         <v>341</v>
       </c>
@@ -8131,6 +9075,11 @@
       <c r="C255" s="62">
         <v>0.3</v>
       </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
     </row>
     <row r="256" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B256" s="3" t="s">
@@ -8140,6 +9089,11 @@
         <f>MACC!$E$38</f>
         <v>50</v>
       </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E256" s="59" t="s">
         <v>59</v>
       </c>
@@ -8155,6 +9109,11 @@
         <f>MACC!$E$36</f>
         <v>15</v>
       </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E257" s="59" t="s">
         <v>53</v>
       </c>
@@ -8170,6 +9129,11 @@
         <f>MACC!$E$42</f>
         <v>0.4</v>
       </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E258" s="59"/>
     </row>
     <row r="259" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -8179,6 +9143,11 @@
       <c r="C259" s="64">
         <v>25</v>
       </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E259" s="59" t="s">
         <v>204</v>
       </c>
@@ -8190,6 +9159,11 @@
       <c r="C260" s="89">
         <v>0.1</v>
       </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E260" s="59"/>
       <c r="F260" s="5" t="s">
         <v>364</v>
@@ -8201,6 +9175,11 @@
       </c>
       <c r="C261" s="89">
         <v>0.6</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E261" s="59"/>
     </row>
@@ -8222,6 +9201,11 @@
         <f>C264*C254</f>
         <v>28215.000000000004</v>
       </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E263" s="59" t="s">
         <v>207</v>
       </c>
@@ -8234,6 +9218,11 @@
         <f>C265*8760*C255/1.163*10^-3</f>
         <v>51300</v>
       </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E264" s="59" t="s">
         <v>367</v>
       </c>
@@ -8246,6 +9235,11 @@
         <f>C249*(1-C260)*C261</f>
         <v>22702.397260273974</v>
       </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E265" s="59" t="s">
         <v>209</v>
       </c>
@@ -8257,6 +9251,11 @@
       <c r="C266" s="65">
         <f>C264*1.163</f>
         <v>59661.9</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E266" s="59" t="s">
         <v>350</v>
@@ -8280,6 +9279,11 @@
         <f>C265*C251/1000</f>
         <v>3405.3595890410961</v>
       </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="269" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B269" s="3" t="s">
@@ -8288,6 +9292,11 @@
       <c r="C269" s="67">
         <f>C268*C252</f>
         <v>1362.1438356164385</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="270" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -8321,6 +9330,11 @@
         <f>C265/(1-C260)*E272*10^-3</f>
         <v>-25.224885844748862</v>
       </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E272" s="72">
         <v>-1</v>
       </c>
@@ -8336,6 +9350,11 @@
         <f>C266*C256/1000</f>
         <v>2983.0949999999998</v>
       </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="274" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B274" s="3" t="s">
@@ -8344,6 +9363,11 @@
       <c r="C274" s="67">
         <f>E274*C257</f>
         <v>-288.5625</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E274" s="72">
         <f>-C263*1000/(C258*44/12)/10^6</f>
@@ -8384,6 +9408,11 @@
         <f>C270</f>
         <v>4767.5034246575342</v>
       </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E277" s="59" t="s">
         <v>224</v>
       </c>
@@ -8396,6 +9425,11 @@
         <f>C275</f>
         <v>2669.307614155251</v>
       </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E278" s="59" t="s">
         <v>226</v>
       </c>
@@ -8408,6 +9442,11 @@
         <f>C259</f>
         <v>25</v>
       </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E279" s="59" t="s">
         <v>204</v>
       </c>
@@ -8420,20 +9459,25 @@
         <f>C263</f>
         <v>28215.000000000004</v>
       </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E280" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="281" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="282" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A282" s="115" t="s">
+      <c r="A282" s="114" t="s">
         <v>371</v>
       </c>
-      <c r="B282" s="115"/>
-      <c r="C282" s="115"/>
-      <c r="D282" s="115"/>
-      <c r="E282" s="115"/>
-      <c r="F282" s="115"/>
+      <c r="B282" s="114"/>
+      <c r="C282" s="114"/>
+      <c r="D282" s="114"/>
+      <c r="E282" s="114"/>
+      <c r="F282" s="114"/>
       <c r="G282" s="55">
         <v>1</v>
       </c>
@@ -8456,6 +9500,11 @@
         <f>Выбросы!C8</f>
         <v>135.30000000000001</v>
       </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E284" s="59" t="s">
         <v>192</v>
       </c>
@@ -8471,6 +9520,11 @@
         <f>MACC!$E$53</f>
         <v>2500</v>
       </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E285" s="59" t="s">
         <v>88</v>
       </c>
@@ -8485,6 +9539,11 @@
       <c r="C286" s="89">
         <v>0.8</v>
       </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E286" s="59"/>
       <c r="F286" s="5"/>
     </row>
@@ -8495,6 +9554,11 @@
       <c r="C287" s="66">
         <v>2500</v>
       </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E287" s="59" t="s">
         <v>209</v>
       </c>
@@ -8510,6 +9574,11 @@
         <f>MACC!$E$36</f>
         <v>15</v>
       </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E288" s="59" t="s">
         <v>53</v>
       </c>
@@ -8525,6 +9594,11 @@
         <f>MACC!$E$42</f>
         <v>0.4</v>
       </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E289" s="59"/>
     </row>
     <row r="290" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -8533,6 +9607,11 @@
       </c>
       <c r="C290" s="64">
         <v>20</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E290" s="59" t="s">
         <v>204</v>
@@ -8556,6 +9635,11 @@
         <f>C287*8760*C286*C37*10^-3</f>
         <v>17520</v>
       </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E292" s="59" t="s">
         <v>207</v>
       </c>
@@ -8578,6 +9662,11 @@
         <f>C285*C287*10^-3</f>
         <v>6250</v>
       </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E294" s="59" t="s">
         <v>224</v>
       </c>
@@ -8618,6 +9707,11 @@
         <f>C296*0.03</f>
         <v>187.5</v>
       </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F298" s="5" t="s">
         <v>379</v>
       </c>
@@ -8629,6 +9723,11 @@
       <c r="C299" s="67">
         <f>-C292*1000/(C289*44/12)*C288/10^6</f>
         <v>-179.18181818181819</v>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="F299" s="5" t="s">
         <v>264</v>
@@ -8665,6 +9764,11 @@
         <f>C296</f>
         <v>6250</v>
       </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E302" s="59" t="s">
         <v>224</v>
       </c>
@@ -8677,6 +9781,11 @@
         <f>C300</f>
         <v>8.318181818181813</v>
       </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E303" s="59" t="s">
         <v>226</v>
       </c>
@@ -8689,6 +9798,11 @@
         <f>C290</f>
         <v>20</v>
       </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E304" s="59" t="s">
         <v>204</v>
       </c>
@@ -8701,20 +9815,25 @@
         <f>C292</f>
         <v>17520</v>
       </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E305" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="306" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="307" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A307" s="115" t="s">
+      <c r="A307" s="114" t="s">
         <v>380</v>
       </c>
-      <c r="B307" s="115"/>
-      <c r="C307" s="115"/>
-      <c r="D307" s="115"/>
-      <c r="E307" s="115"/>
-      <c r="F307" s="115"/>
+      <c r="B307" s="114"/>
+      <c r="C307" s="114"/>
+      <c r="D307" s="114"/>
+      <c r="E307" s="114"/>
+      <c r="F307" s="114"/>
       <c r="G307" s="55">
         <v>1</v>
       </c>
@@ -8737,6 +9856,11 @@
         <f>Выбросы!C10</f>
         <v>27.1</v>
       </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E309" s="59" t="s">
         <v>192</v>
       </c>
@@ -8751,6 +9875,11 @@
       <c r="C310" s="4">
         <v>0.15</v>
       </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F310" s="5" t="s">
         <v>228</v>
       </c>
@@ -8763,6 +9892,11 @@
         <f>MACC!$E$54</f>
         <v>5000</v>
       </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E311" s="59" t="s">
         <v>90</v>
       </c>
@@ -8777,6 +9911,11 @@
       <c r="C312" s="66">
         <v>15000</v>
       </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E312" s="59" t="s">
         <v>385</v>
       </c>
@@ -8788,6 +9927,11 @@
       <c r="C313" s="87">
         <v>8</v>
       </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E313" s="59" t="s">
         <v>387</v>
       </c>
@@ -8799,6 +9943,11 @@
       <c r="C314" s="62">
         <v>0.5</v>
       </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E314" s="59" t="s">
         <v>389</v>
       </c>
@@ -8813,6 +9962,11 @@
       <c r="C315" s="62">
         <v>60</v>
       </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E315" s="59" t="s">
         <v>59</v>
       </c>
@@ -8827,6 +9981,11 @@
       <c r="C316" s="62">
         <v>18</v>
       </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E316" s="59" t="s">
         <v>393</v>
       </c>
@@ -8839,6 +9998,11 @@
       <c r="C317" s="62">
         <v>2.31</v>
       </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E317" s="59" t="s">
         <v>395</v>
       </c>
@@ -8852,6 +10016,11 @@
       </c>
       <c r="C318" s="64">
         <v>15</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E318" s="59" t="s">
         <v>204</v>
@@ -8880,6 +10049,11 @@
         <f>C309*C310*1000</f>
         <v>4065.0000000000005</v>
       </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E321" s="59" t="s">
         <v>207</v>
       </c>
@@ -8892,6 +10066,11 @@
         <f>C325*1000*C312*C313/100*10^-6</f>
         <v>1759.7402597402599</v>
       </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E322" s="59" t="s">
         <v>399</v>
       </c>
@@ -8904,6 +10083,11 @@
         <f>C312*C325*C316/100*10^-6</f>
         <v>3.9594155844155847</v>
       </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E323" s="59" t="s">
         <v>401</v>
       </c>
@@ -8916,6 +10100,11 @@
         <f>0.95*0.5*C323*1000</f>
         <v>1880.7224025974028</v>
       </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E324" s="59" t="s">
         <v>207</v>
       </c>
@@ -8927,6 +10116,11 @@
       <c r="C325" s="65">
         <f>C321*1000/(C312*C313/100*C317)</f>
         <v>1466.4502164502167</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E325" s="59" t="s">
         <v>404</v>
@@ -8951,6 +10145,11 @@
         <f>C325*C311/10^3</f>
         <v>7332.2510822510831</v>
       </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E327" s="59" t="s">
         <v>224</v>
       </c>
@@ -8962,6 +10161,11 @@
       <c r="C328" s="67">
         <f>C325*1000/10^3</f>
         <v>1466.4502164502167</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E328" s="59" t="s">
         <v>224</v>
@@ -9001,6 +10205,11 @@
         <f>C323*C315</f>
         <v>237.56493506493507</v>
       </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E331" s="59" t="s">
         <v>224</v>
       </c>
@@ -9012,6 +10221,11 @@
       <c r="C332" s="67">
         <f>-C325*1000*C312*C313/100*C314/10^6</f>
         <v>-879.87012987013009</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="333" spans="1:9" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -9045,6 +10259,11 @@
         <f>C329</f>
         <v>8798.7012987013004</v>
       </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E335" s="59" t="s">
         <v>224</v>
       </c>
@@ -9057,6 +10276,11 @@
         <f>C333</f>
         <v>-642.30519480519501</v>
       </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E336" s="59" t="s">
         <v>226</v>
       </c>
@@ -9069,6 +10293,11 @@
         <f>C318</f>
         <v>15</v>
       </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E337" s="59" t="s">
         <v>204</v>
       </c>
@@ -9081,25 +10310,30 @@
         <f>C321-C324</f>
         <v>2184.2775974025976</v>
       </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E338" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="339" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="340" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A340" s="115" t="s">
+      <c r="A340" s="114" t="s">
         <v>410</v>
       </c>
-      <c r="B340" s="115"/>
-      <c r="C340" s="115"/>
-      <c r="D340" s="115"/>
-      <c r="E340" s="115"/>
-      <c r="F340" s="115"/>
+      <c r="B340" s="114"/>
+      <c r="C340" s="114"/>
+      <c r="D340" s="114"/>
+      <c r="E340" s="114"/>
+      <c r="F340" s="114"/>
       <c r="G340" s="55">
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A341" s="56"/>
       <c r="B341" s="57" t="s">
         <v>190</v>
@@ -9109,7 +10343,7 @@
       <c r="E341" s="56"/>
       <c r="F341" s="56"/>
     </row>
-    <row r="342" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B342" s="3" t="s">
         <v>411</v>
       </c>
@@ -9117,6 +10351,11 @@
         <f>Выбросы!C11+Выбросы!C8*0.2</f>
         <v>73.56</v>
       </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E342" s="59" t="s">
         <v>192</v>
       </c>
@@ -9124,7 +10363,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B343" s="3" t="s">
         <v>194</v>
       </c>
@@ -9132,11 +10371,16 @@
         <f>C362/C342*10^-3</f>
         <v>0.12530235697811781</v>
       </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F343" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B344" s="3" t="s">
         <v>412</v>
       </c>
@@ -9144,6 +10388,11 @@
         <f>MACC!$E$55</f>
         <v>100</v>
       </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E344" s="59" t="s">
         <v>93</v>
       </c>
@@ -9151,7 +10400,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B345" s="3" t="s">
         <v>414</v>
       </c>
@@ -9159,6 +10408,11 @@
         <f>M355</f>
         <v>3375</v>
       </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E345" s="59" t="s">
         <v>415</v>
       </c>
@@ -9166,13 +10420,18 @@
         <v>416</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B346" s="3" t="s">
         <v>417</v>
       </c>
       <c r="C346" s="66">
         <v>50</v>
       </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E346" s="59" t="s">
         <v>404</v>
       </c>
@@ -9180,18 +10439,23 @@
         <v>418</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B347" s="3" t="s">
         <v>419</v>
       </c>
       <c r="C347" s="4">
         <v>0.5</v>
       </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F347" s="5" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B348" s="3" t="s">
         <v>421</v>
       </c>
@@ -9199,21 +10463,31 @@
         <f>C346*C345*10^3*C357*10^-6/(1-C358)</f>
         <v>48600</v>
       </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E348" s="59" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B349" s="3"/>
       <c r="C349" s="66">
         <f>C348/1.16</f>
         <v>41896.551724137935</v>
       </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E349" s="59" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B350" s="3" t="s">
         <v>423</v>
       </c>
@@ -9221,21 +10495,31 @@
         <f>C348*(1-C347)</f>
         <v>24300</v>
       </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E350" s="59" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B351" s="3"/>
       <c r="C351" s="66">
         <f>C350/1.16</f>
         <v>20948.275862068967</v>
       </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E351" s="59" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B352" s="3" t="s">
         <v>64</v>
       </c>
@@ -9243,22 +10527,32 @@
         <f>MACC!$E$41</f>
         <v>0.55000000000000004</v>
       </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E352" s="59" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="353" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B353" s="3" t="s">
         <v>203</v>
       </c>
       <c r="C353" s="64">
         <v>30</v>
       </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E353" s="59" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="354" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B354" s="3" t="s">
         <v>424</v>
       </c>
@@ -9266,6 +10560,11 @@
         <f>(H355+I355)*(J355)*2/(H355*I355*K355)</f>
         <v>0.53333333333333333</v>
       </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E354" s="59"/>
       <c r="H354" s="1" t="s">
         <v>425</v>
@@ -9280,7 +10579,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="355" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B355" s="3" t="s">
         <v>342</v>
       </c>
@@ -9288,6 +10587,11 @@
         <f>MACC!$E$42</f>
         <v>0.4</v>
       </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E355" s="59"/>
       <c r="H355" s="1">
         <v>15</v>
@@ -9307,7 +10611,7 @@
         <v>3375</v>
       </c>
     </row>
-    <row r="356" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B356" s="3" t="s">
         <v>52</v>
       </c>
@@ -9315,11 +10619,16 @@
         <f>MACC!$E$36</f>
         <v>15</v>
       </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E356" s="59" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="357" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B357" s="3" t="s">
         <v>430</v>
       </c>
@@ -9327,6 +10636,11 @@
         <f>240*(1-0.1)</f>
         <v>216</v>
       </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E357" s="59" t="s">
         <v>431</v>
       </c>
@@ -9334,32 +10648,42 @@
         <v>432</v>
       </c>
     </row>
-    <row r="358" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B358" s="3" t="s">
         <v>433</v>
       </c>
       <c r="C358" s="89">
         <v>0.25</v>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E358" s="59"/>
       <c r="F358" s="5" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="359" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B359" s="3" t="s">
         <v>435</v>
       </c>
       <c r="C359" s="89">
         <v>0.2</v>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E359" s="59"/>
       <c r="F359" s="5" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="360" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35"/>
-    <row r="361" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="361" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A361" s="56"/>
       <c r="B361" s="57" t="s">
         <v>205</v>
@@ -9369,7 +10693,7 @@
       <c r="E361" s="56"/>
       <c r="F361" s="56"/>
     </row>
-    <row r="362" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B362" s="3" t="s">
         <v>206</v>
       </c>
@@ -9377,11 +10701,16 @@
         <f>-(C351-C349)*C352*(1-C359)</f>
         <v>9217.241379310346</v>
       </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E362" s="59" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="363" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A363" s="56"/>
       <c r="B363" s="57" t="s">
         <v>211</v>
@@ -9391,7 +10720,7 @@
       <c r="E363" s="56"/>
       <c r="F363" s="56"/>
     </row>
-    <row r="364" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B364" s="3" t="s">
         <v>437</v>
       </c>
@@ -9399,8 +10728,13 @@
         <f>C346*1000*C345*C344*C354/10^6</f>
         <v>9000</v>
       </c>
-    </row>
-    <row r="365" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B365" s="3" t="s">
         <v>438</v>
       </c>
@@ -9408,11 +10742,16 @@
         <f>C364*0.2</f>
         <v>1800</v>
       </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F365" s="5" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="366" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A366" s="68"/>
       <c r="B366" s="69" t="s">
         <v>215</v>
@@ -9425,7 +10764,7 @@
       <c r="E366" s="68"/>
       <c r="F366" s="68"/>
     </row>
-    <row r="367" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A367" s="56"/>
       <c r="B367" s="57" t="s">
         <v>216</v>
@@ -9435,7 +10774,7 @@
       <c r="E367" s="56"/>
       <c r="F367" s="56"/>
     </row>
-    <row r="368" spans="1:13" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:13" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B368" s="92" t="s">
         <v>440</v>
       </c>
@@ -9443,8 +10782,13 @@
         <f>C366*0.005</f>
         <v>54</v>
       </c>
-    </row>
-    <row r="369" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B369" s="92" t="s">
         <v>441</v>
       </c>
@@ -9452,6 +10796,11 @@
         <f>C350*E369*10^-3</f>
         <v>-729</v>
       </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E369" s="1">
         <v>-30</v>
       </c>
@@ -9459,7 +10808,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="370" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B370" s="92" t="s">
         <v>443</v>
       </c>
@@ -9467,6 +10816,11 @@
         <f>E370*C356</f>
         <v>-94.267241379310349</v>
       </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E370" s="72">
         <f>-C362*1000/(C355*44/12)/10^6</f>
         <v>-6.2844827586206895</v>
@@ -9475,7 +10829,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="371" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A371" s="68"/>
       <c r="B371" s="69" t="s">
         <v>221</v>
@@ -9488,7 +10842,7 @@
       <c r="E371" s="68"/>
       <c r="F371" s="68"/>
     </row>
-    <row r="372" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A372" s="56"/>
       <c r="B372" s="57" t="s">
         <v>222</v>
@@ -9498,7 +10852,7 @@
       <c r="E372" s="56"/>
       <c r="F372" s="56"/>
     </row>
-    <row r="373" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B373" s="73" t="s">
         <v>223</v>
       </c>
@@ -9506,11 +10860,16 @@
         <f>C366</f>
         <v>10800</v>
       </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E373" s="59" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="374" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B374" s="73" t="s">
         <v>225</v>
       </c>
@@ -9518,11 +10877,16 @@
         <f>C371</f>
         <v>-769.26724137931035</v>
       </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E374" s="59" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="375" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B375" s="73" t="s">
         <v>203</v>
       </c>
@@ -9530,11 +10894,16 @@
         <f>C353</f>
         <v>30</v>
       </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E375" s="59" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="376" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B376" s="73" t="s">
         <v>206</v>
       </c>
@@ -9542,19 +10911,25 @@
         <f>C362</f>
         <v>9217.241379310346</v>
       </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E376" s="59" t="s">
         <v>207</v>
       </c>
     </row>
+    <row r="377" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="378" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A378" s="115" t="s">
+      <c r="A378" s="114" t="s">
         <v>444</v>
       </c>
-      <c r="B378" s="115"/>
-      <c r="C378" s="115"/>
-      <c r="D378" s="115"/>
-      <c r="E378" s="115"/>
-      <c r="F378" s="115"/>
+      <c r="B378" s="114"/>
+      <c r="C378" s="114"/>
+      <c r="D378" s="114"/>
+      <c r="E378" s="114"/>
+      <c r="F378" s="114"/>
       <c r="G378" s="55">
         <v>1</v>
       </c>
@@ -9577,6 +10952,11 @@
         <f>Выбросы!C11</f>
         <v>46.5</v>
       </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E380" s="59" t="s">
         <v>192</v>
       </c>
@@ -9591,6 +10971,11 @@
       <c r="C381" s="4">
         <v>0.15</v>
       </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F381" s="5" t="s">
         <v>228</v>
       </c>
@@ -9602,6 +10987,11 @@
       <c r="C382" s="66">
         <v>5000</v>
       </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E382" s="59" t="s">
         <v>446</v>
       </c>
@@ -9616,6 +11006,11 @@
       <c r="C383" s="87">
         <v>0.5</v>
       </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E383" s="59" t="s">
         <v>449</v>
       </c>
@@ -9627,6 +11022,11 @@
       <c r="C384" s="66">
         <v>300</v>
       </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E384" s="59" t="s">
         <v>404</v>
       </c>
@@ -9638,6 +11038,11 @@
       <c r="C385" s="66">
         <v>2</v>
       </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E385" s="59" t="s">
         <v>452</v>
       </c>
@@ -9650,6 +11055,11 @@
         <f>MACC!$E$36</f>
         <v>15</v>
       </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E386" s="59" t="s">
         <v>53</v>
       </c>
@@ -9665,6 +11075,11 @@
         <f>MACC!$E$37</f>
         <v>250</v>
       </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E387" s="59" t="s">
         <v>454</v>
       </c>
@@ -9676,6 +11091,11 @@
       <c r="C388" s="64">
         <v>30</v>
       </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E388" s="59" t="s">
         <v>204</v>
       </c>
@@ -9686,6 +11106,11 @@
       </c>
       <c r="C389" s="64">
         <v>12</v>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E389" s="59" t="s">
         <v>456</v>
@@ -9709,6 +11134,11 @@
         <f>C380*C381*1000</f>
         <v>6975</v>
       </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E391" s="59" t="s">
         <v>207</v>
       </c>
@@ -9721,6 +11151,11 @@
         <f>C389*C384*10^-3</f>
         <v>3.6</v>
       </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E392" s="59" t="s">
         <v>457</v>
       </c>
@@ -9732,6 +11167,11 @@
       <c r="C393" s="65">
         <f>C392*10^9*8180/4000*10^-9</f>
         <v>7.3620000000000001</v>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E393" s="59" t="s">
         <v>459</v>
@@ -9755,6 +11195,11 @@
         <f>C382*C383</f>
         <v>2500</v>
       </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="396" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B396" s="3" t="s">
@@ -9763,6 +11208,11 @@
       <c r="C396" s="67">
         <f>C384*C385/10^3</f>
         <v>0.6</v>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="397" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -9796,6 +11246,11 @@
         <f>C397*0.03</f>
         <v>75.018000000000001</v>
       </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E399" s="88">
         <v>0.03</v>
       </c>
@@ -9811,6 +11266,11 @@
         <f>C392*C387</f>
         <v>900</v>
       </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E400" s="59" t="s">
         <v>224</v>
       </c>
@@ -9822,6 +11282,11 @@
       <c r="C401" s="67">
         <f>-C393*C386</f>
         <v>-110.43</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E401" s="59" t="s">
         <v>224</v>
@@ -9858,6 +11323,11 @@
         <f>C397</f>
         <v>2500.6</v>
       </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E404" s="59" t="s">
         <v>224</v>
       </c>
@@ -9870,6 +11340,11 @@
         <f>C402</f>
         <v>864.58799999999997</v>
       </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E405" s="59" t="s">
         <v>226</v>
       </c>
@@ -9882,6 +11357,11 @@
         <f>C388</f>
         <v>30</v>
       </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E406" s="59" t="s">
         <v>204</v>
       </c>
@@ -9894,20 +11374,25 @@
         <f>C391</f>
         <v>6975</v>
       </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E407" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="408" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="409" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A409" s="115" t="s">
+      <c r="A409" s="114" t="s">
         <v>464</v>
       </c>
-      <c r="B409" s="115"/>
-      <c r="C409" s="115"/>
-      <c r="D409" s="115"/>
-      <c r="E409" s="115"/>
-      <c r="F409" s="115"/>
+      <c r="B409" s="114"/>
+      <c r="C409" s="114"/>
+      <c r="D409" s="114"/>
+      <c r="E409" s="114"/>
+      <c r="F409" s="114"/>
       <c r="G409" s="55">
         <v>1</v>
       </c>
@@ -9930,6 +11415,11 @@
         <f>Выбросы!C11</f>
         <v>46.5</v>
       </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E411" s="59" t="s">
         <v>192</v>
       </c>
@@ -9944,6 +11434,11 @@
       <c r="C412" s="4">
         <v>0.5</v>
       </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E412" s="59"/>
       <c r="F412" s="5"/>
     </row>
@@ -9954,6 +11449,11 @@
       <c r="C413" s="77">
         <v>0.5</v>
       </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F413" s="5"/>
     </row>
     <row r="414" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -9964,6 +11464,11 @@
         <f>MACC!$E$52</f>
         <v>150</v>
       </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E414" s="59" t="s">
         <v>72</v>
       </c>
@@ -9978,6 +11483,11 @@
       <c r="C415" s="4">
         <v>0.4</v>
       </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E415" s="59" t="s">
         <v>359</v>
       </c>
@@ -9989,6 +11499,11 @@
       <c r="C416" s="4">
         <v>0.3</v>
       </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E416" s="59" t="s">
         <v>359</v>
       </c>
@@ -10000,6 +11515,11 @@
       <c r="C417" s="66">
         <v>30</v>
       </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E417" s="59" t="s">
         <v>469</v>
       </c>
@@ -10014,6 +11534,11 @@
       <c r="C418" s="66">
         <v>180</v>
       </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E418" s="59" t="s">
         <v>340</v>
       </c>
@@ -10026,6 +11551,11 @@
         <f>MACC!$E$41</f>
         <v>0.55000000000000004</v>
       </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E419" s="59" t="s">
         <v>341</v>
       </c>
@@ -10038,6 +11568,11 @@
         <f>MACC!$E$42</f>
         <v>0.4</v>
       </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E420" s="59"/>
     </row>
     <row r="421" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -10047,6 +11582,11 @@
       <c r="C421" s="62">
         <v>0.3</v>
       </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
     </row>
     <row r="422" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B422" s="3" t="s">
@@ -10055,6 +11595,11 @@
       <c r="C422" s="66">
         <v>50</v>
       </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E422" s="59" t="s">
         <v>59</v>
       </c>
@@ -10067,6 +11612,11 @@
         <f>MACC!$E$36</f>
         <v>15</v>
       </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E423" s="59" t="s">
         <v>429</v>
       </c>
@@ -10078,6 +11628,11 @@
       <c r="C424" s="64">
         <v>25</v>
       </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E424" s="59" t="s">
         <v>204</v>
       </c>
@@ -10088,6 +11643,11 @@
       </c>
       <c r="C425" s="89">
         <v>0.1</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E425" s="59"/>
       <c r="F425" s="5" t="s">
@@ -10112,6 +11672,11 @@
         <f>C411*C412*C413*10^3</f>
         <v>11625</v>
       </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E427" s="59" t="s">
         <v>207</v>
       </c>
@@ -10124,6 +11689,11 @@
         <f>C427/C419</f>
         <v>21136.363636363636</v>
       </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E428" s="59" t="s">
         <v>367</v>
       </c>
@@ -10136,6 +11706,11 @@
         <f>C428*1000*1.163/(8760*C421)</f>
         <v>9353.7256122872568</v>
       </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E429" s="59" t="s">
         <v>209</v>
       </c>
@@ -10147,6 +11722,11 @@
       <c r="C430" s="65">
         <f>C428*1.163</f>
         <v>24581.590909090908</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E430" s="59" t="s">
         <v>350</v>
@@ -10170,6 +11750,11 @@
         <f>C429*C414/1000</f>
         <v>1403.0588418430887</v>
       </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="433" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B433" s="3" t="s">
@@ -10179,6 +11764,11 @@
         <f>C432*C415</f>
         <v>561.22353673723546</v>
       </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="434" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B434" s="3" t="s">
@@ -10188,6 +11778,11 @@
         <f>C432*C416</f>
         <v>420.9176525529266</v>
       </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="435" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B435" s="3" t="s">
@@ -10196,6 +11791,11 @@
       <c r="C435" s="67">
         <f>PV(MACC!$C$2,C424,C417*C429/1000)</f>
         <v>-2200.8771357975043</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
       </c>
     </row>
     <row r="436" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -10229,6 +11829,11 @@
         <f>C432*0.02</f>
         <v>28.061176836861772</v>
       </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="439" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B439" s="3" t="s">
@@ -10238,6 +11843,11 @@
         <f>C430*C422/1000</f>
         <v>1229.0795454545455</v>
       </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="440" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B440" s="3" t="s">
@@ -10246,6 +11856,11 @@
       <c r="C440" s="67">
         <f>E440*C423</f>
         <v>-118.89204545454545</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E440" s="72">
         <f>-C427*1000/(C420*44/12)/10^6</f>
@@ -10286,6 +11901,11 @@
         <f>C436</f>
         <v>184.32289533574658</v>
       </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E443" s="59" t="s">
         <v>224</v>
       </c>
@@ -10298,6 +11918,11 @@
         <f>C441</f>
         <v>1138.2486768368617</v>
       </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E444" s="59" t="s">
         <v>226</v>
       </c>
@@ -10310,6 +11935,11 @@
         <f>C424</f>
         <v>25</v>
       </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E445" s="59" t="s">
         <v>204</v>
       </c>
@@ -10322,20 +11952,25 @@
         <f>C427</f>
         <v>11625</v>
       </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E446" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="447" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="448" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A448" s="115" t="s">
+      <c r="A448" s="114" t="s">
         <v>475</v>
       </c>
-      <c r="B448" s="115"/>
-      <c r="C448" s="115"/>
-      <c r="D448" s="115"/>
-      <c r="E448" s="115"/>
-      <c r="F448" s="115"/>
+      <c r="B448" s="114"/>
+      <c r="C448" s="114"/>
+      <c r="D448" s="114"/>
+      <c r="E448" s="114"/>
+      <c r="F448" s="114"/>
       <c r="G448" s="94">
         <v>2</v>
       </c>
@@ -10358,6 +11993,11 @@
         <f>Выбросы!C15</f>
         <v>34.200000000000003</v>
       </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E450" s="59" t="s">
         <v>192</v>
       </c>
@@ -10372,6 +12012,11 @@
       <c r="C451" s="4">
         <v>0.25</v>
       </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F451" s="5" t="s">
         <v>228</v>
       </c>
@@ -10383,6 +12028,11 @@
       <c r="C452" s="66">
         <v>5000</v>
       </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E452" s="59" t="s">
         <v>478</v>
       </c>
@@ -10397,6 +12047,11 @@
       <c r="C453" s="66">
         <v>8</v>
       </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E453" s="59" t="s">
         <v>481</v>
       </c>
@@ -10411,6 +12066,11 @@
       <c r="C454" s="66">
         <v>3</v>
       </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E454" s="59" t="s">
         <v>481</v>
       </c>
@@ -10425,6 +12085,11 @@
       <c r="C455" s="66">
         <v>2</v>
       </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E455" s="59" t="s">
         <v>486</v>
       </c>
@@ -10439,6 +12104,11 @@
       <c r="C456" s="66">
         <v>1.5</v>
       </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E456" s="59" t="s">
         <v>486</v>
       </c>
@@ -10452,6 +12122,11 @@
       </c>
       <c r="C457" s="64">
         <v>10</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E457" s="59" t="s">
         <v>204</v>
@@ -10475,6 +12150,11 @@
         <f>C450*C451*1000</f>
         <v>8550</v>
       </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E459" s="59" t="s">
         <v>207</v>
       </c>
@@ -10497,6 +12177,11 @@
         <f>C452*C453/10^3</f>
         <v>40</v>
       </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="462" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B462" s="3" t="s">
@@ -10505,6 +12190,11 @@
       <c r="C462" s="67">
         <f>C452*C454/10^3</f>
         <v>15</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="463" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -10538,6 +12228,11 @@
         <f>C452*C455/10^3</f>
         <v>10</v>
       </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="466" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B466" s="3" t="s">
@@ -10546,6 +12241,11 @@
       <c r="C466" s="67">
         <f>-C452*C456/10^3</f>
         <v>-7.5</v>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="467" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -10579,6 +12279,11 @@
         <f>C463</f>
         <v>55</v>
       </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E469" s="59" t="s">
         <v>224</v>
       </c>
@@ -10591,6 +12296,11 @@
         <f>C467</f>
         <v>2.5</v>
       </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E470" s="59" t="s">
         <v>226</v>
       </c>
@@ -10603,6 +12313,11 @@
         <f>C457</f>
         <v>10</v>
       </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E471" s="59" t="s">
         <v>204</v>
       </c>
@@ -10615,20 +12330,25 @@
         <f>C459</f>
         <v>8550</v>
       </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E472" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="473" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="474" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A474" s="115" t="s">
+      <c r="A474" s="114" t="s">
         <v>494</v>
       </c>
-      <c r="B474" s="115"/>
-      <c r="C474" s="115"/>
-      <c r="D474" s="115"/>
-      <c r="E474" s="115"/>
-      <c r="F474" s="115"/>
+      <c r="B474" s="114"/>
+      <c r="C474" s="114"/>
+      <c r="D474" s="114"/>
+      <c r="E474" s="114"/>
+      <c r="F474" s="114"/>
       <c r="G474" s="94">
         <v>2</v>
       </c>
@@ -10651,6 +12371,11 @@
         <f>Выбросы!C15</f>
         <v>34.200000000000003</v>
       </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E476" s="59" t="s">
         <v>192</v>
       </c>
@@ -10665,6 +12390,11 @@
       <c r="C477" s="4">
         <v>0.2</v>
       </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F477" s="5" t="s">
         <v>228</v>
       </c>
@@ -10676,6 +12406,11 @@
       <c r="C478" s="66">
         <v>3</v>
       </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E478" s="59" t="s">
         <v>496</v>
       </c>
@@ -10690,6 +12425,11 @@
       <c r="C479" s="66">
         <v>500</v>
       </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E479" s="59" t="s">
         <v>499</v>
       </c>
@@ -10704,6 +12444,11 @@
       <c r="C480" s="66">
         <v>40</v>
       </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E480" s="59" t="s">
         <v>59</v>
       </c>
@@ -10717,6 +12462,11 @@
       </c>
       <c r="C481" s="64">
         <v>20</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E481" s="59" t="s">
         <v>204</v>
@@ -10740,6 +12490,11 @@
         <f>C476*C477*1000</f>
         <v>6840.0000000000009</v>
       </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E483" s="59" t="s">
         <v>207</v>
       </c>
@@ -10751,6 +12506,11 @@
       <c r="C484" s="65">
         <f>C478*10^9*10/(3600*10^3)</f>
         <v>8333.3333333333339</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E484" s="59" t="s">
         <v>350</v>
@@ -10774,6 +12534,11 @@
         <f>C478*10^6*C479/10^6</f>
         <v>1500</v>
       </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="487" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B487" s="3" t="s">
@@ -10782,6 +12547,11 @@
       <c r="C487" s="67">
         <f>C486*0.25</f>
         <v>375</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="488" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -10815,6 +12585,11 @@
         <f>C488*0.03</f>
         <v>56.25</v>
       </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="491" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B491" s="3" t="s">
@@ -10823,6 +12598,11 @@
       <c r="C491" s="67">
         <f>-C484*C480/1000</f>
         <v>-333.33333333333337</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="492" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -10856,6 +12636,11 @@
         <f>C488</f>
         <v>1875</v>
       </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E494" s="59" t="s">
         <v>224</v>
       </c>
@@ -10868,6 +12653,11 @@
         <f>C492</f>
         <v>-277.08333333333337</v>
       </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E495" s="59" t="s">
         <v>226</v>
       </c>
@@ -10880,6 +12670,11 @@
         <f>C481</f>
         <v>20</v>
       </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E496" s="59" t="s">
         <v>204</v>
       </c>
@@ -10892,20 +12687,25 @@
         <f>C483</f>
         <v>6840.0000000000009</v>
       </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E497" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="498" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="499" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A499" s="115" t="s">
+      <c r="A499" s="114" t="s">
         <v>507</v>
       </c>
-      <c r="B499" s="115"/>
-      <c r="C499" s="115"/>
-      <c r="D499" s="115"/>
-      <c r="E499" s="115"/>
-      <c r="F499" s="115"/>
+      <c r="B499" s="114"/>
+      <c r="C499" s="114"/>
+      <c r="D499" s="114"/>
+      <c r="E499" s="114"/>
+      <c r="F499" s="114"/>
       <c r="G499" s="55">
         <v>1</v>
       </c>
@@ -10928,6 +12728,11 @@
         <f>Выбросы!C14</f>
         <v>9.5</v>
       </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E501" s="59" t="s">
         <v>192</v>
       </c>
@@ -10942,6 +12747,11 @@
       <c r="C502" s="4">
         <v>0.2</v>
       </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F502" s="5" t="s">
         <v>228</v>
       </c>
@@ -10953,6 +12763,11 @@
       <c r="C503" s="66">
         <v>300</v>
       </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E503" s="59" t="s">
         <v>224</v>
       </c>
@@ -10968,6 +12783,11 @@
         <f>C509*C505*10^-3</f>
         <v>1.4687693259121835</v>
       </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E504" s="59" t="s">
         <v>226</v>
       </c>
@@ -10982,6 +12802,11 @@
       <c r="C505" s="66">
         <v>150</v>
       </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E505" s="59" t="s">
         <v>283</v>
       </c>
@@ -10993,6 +12818,11 @@
       </c>
       <c r="C506" s="64">
         <v>20</v>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E506" s="59" t="s">
         <v>204</v>
@@ -11016,6 +12846,11 @@
         <f>C501*C502*1000</f>
         <v>1900.0000000000002</v>
       </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E508" s="59" t="s">
         <v>207</v>
       </c>
@@ -11027,6 +12862,11 @@
       <c r="C509" s="95">
         <f>C508/98/(12+16*2)*12/12*16/0.72</f>
         <v>9.7917955060812218</v>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E509" s="59" t="s">
         <v>243</v>
@@ -11050,6 +12890,11 @@
         <f>C503</f>
         <v>300</v>
       </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="512" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A512" s="68"/>
@@ -11082,6 +12927,11 @@
         <f>C512*0.04</f>
         <v>12</v>
       </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="515" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B515" s="3" t="s">
@@ -11090,6 +12940,11 @@
       <c r="C515" s="67">
         <f>-C504</f>
         <v>-1.4687693259121835</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="516" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -11123,6 +12978,11 @@
         <f>C512</f>
         <v>300</v>
       </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E518" s="59" t="s">
         <v>224</v>
       </c>
@@ -11135,6 +12995,11 @@
         <f>C516</f>
         <v>10.531230674087816</v>
       </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E519" s="59" t="s">
         <v>226</v>
       </c>
@@ -11147,6 +13012,11 @@
         <f>C506</f>
         <v>20</v>
       </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E520" s="59" t="s">
         <v>204</v>
       </c>
@@ -11159,20 +13029,25 @@
         <f>C508</f>
         <v>1900.0000000000002</v>
       </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E521" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="522" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="523" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A523" s="115" t="s">
+      <c r="A523" s="114" t="s">
         <v>516</v>
       </c>
-      <c r="B523" s="115"/>
-      <c r="C523" s="115"/>
-      <c r="D523" s="115"/>
-      <c r="E523" s="115"/>
-      <c r="F523" s="115"/>
+      <c r="B523" s="114"/>
+      <c r="C523" s="114"/>
+      <c r="D523" s="114"/>
+      <c r="E523" s="114"/>
+      <c r="F523" s="114"/>
       <c r="G523" s="55">
         <v>1</v>
       </c>
@@ -11195,6 +13070,11 @@
         <f>Выбросы!C15</f>
         <v>34.200000000000003</v>
       </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E525" s="59" t="s">
         <v>192</v>
       </c>
@@ -11209,6 +13089,11 @@
       <c r="C526" s="4">
         <v>0.15</v>
       </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F526" s="5" t="s">
         <v>228</v>
       </c>
@@ -11220,6 +13105,11 @@
       <c r="C527" s="66">
         <v>20000</v>
       </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E527" s="59" t="s">
         <v>446</v>
       </c>
@@ -11234,13 +13124,23 @@
       <c r="C528" s="4">
         <v>0.3</v>
       </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
     </row>
     <row r="529" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B529" s="3" t="s">
-        <v>198</v>
+        <v>668</v>
       </c>
       <c r="C529" s="87">
         <v>0.1</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E529" s="59" t="s">
         <v>449</v>
@@ -11257,6 +13157,11 @@
         <f>MACC!$E$37</f>
         <v>250</v>
       </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E530" s="59" t="s">
         <v>283</v>
       </c>
@@ -11268,6 +13173,11 @@
       </c>
       <c r="C531" s="64">
         <v>20</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E531" s="59" t="s">
         <v>204</v>
@@ -11291,6 +13201,11 @@
         <f>C525*C526*1000</f>
         <v>5130</v>
       </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E533" s="59" t="s">
         <v>207</v>
       </c>
@@ -11302,6 +13217,11 @@
       <c r="C534" s="67">
         <f>C533/(12+16*2)*12/12*16*0.72*10^-3</f>
         <v>1.3431272727272727</v>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E534" s="59" t="s">
         <v>457</v>
@@ -11325,6 +13245,11 @@
         <f>C527*C528*C529</f>
         <v>600</v>
       </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="537" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B537" s="3" t="s">
@@ -11333,6 +13258,11 @@
       <c r="C537" s="67">
         <f>30</f>
         <v>30</v>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="F537" s="5" t="s">
         <v>224</v>
@@ -11369,6 +13299,11 @@
         <f>C538*0.03</f>
         <v>18.899999999999999</v>
       </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="541" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B541" s="3" t="s">
@@ -11377,6 +13312,11 @@
       <c r="C541" s="67">
         <f>C530*C534</f>
         <v>335.78181818181815</v>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E541" s="59" t="s">
         <v>224</v>
@@ -11413,6 +13353,11 @@
         <f>C538</f>
         <v>630</v>
       </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E544" s="59" t="s">
         <v>224</v>
       </c>
@@ -11425,6 +13370,11 @@
         <f>C542</f>
         <v>354.68181818181813</v>
       </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E545" s="59" t="s">
         <v>226</v>
       </c>
@@ -11437,6 +13387,11 @@
         <f>C531</f>
         <v>20</v>
       </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E546" s="59" t="s">
         <v>204</v>
       </c>
@@ -11449,20 +13404,25 @@
         <f>C533</f>
         <v>5130</v>
       </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E547" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="548" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="549" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A549" s="115" t="s">
+      <c r="A549" s="114" t="s">
         <v>526</v>
       </c>
-      <c r="B549" s="115"/>
-      <c r="C549" s="115"/>
-      <c r="D549" s="115"/>
-      <c r="E549" s="115"/>
-      <c r="F549" s="115"/>
+      <c r="B549" s="114"/>
+      <c r="C549" s="114"/>
+      <c r="D549" s="114"/>
+      <c r="E549" s="114"/>
+      <c r="F549" s="114"/>
       <c r="G549" s="96">
         <v>3</v>
       </c>
@@ -11485,6 +13445,11 @@
         <f>Выбросы!C17</f>
         <v>8.6</v>
       </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E551" s="59" t="s">
         <v>192</v>
       </c>
@@ -11499,6 +13464,11 @@
       <c r="C552" s="4">
         <v>0.1</v>
       </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F552" s="5" t="s">
         <v>228</v>
       </c>
@@ -11510,16 +13480,26 @@
       <c r="C553" s="66">
         <v>4</v>
       </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E553" s="59" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="554" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B554" s="3" t="s">
-        <v>198</v>
+        <v>669</v>
       </c>
       <c r="C554" s="66">
         <v>50</v>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E554" s="59" t="s">
         <v>529</v>
@@ -11535,6 +13515,11 @@
       <c r="C555" s="66">
         <v>20</v>
       </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E555" s="59" t="s">
         <v>53</v>
       </c>
@@ -11549,6 +13534,11 @@
       <c r="C556" s="66">
         <v>10</v>
       </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E556" s="59" t="s">
         <v>534</v>
       </c>
@@ -11563,6 +13553,11 @@
       <c r="C557" s="66">
         <v>10</v>
       </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E557" s="59" t="s">
         <v>537</v>
       </c>
@@ -11576,6 +13571,11 @@
       </c>
       <c r="C558" s="64">
         <v>30</v>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E558" s="59" t="s">
         <v>204</v>
@@ -11599,6 +13599,11 @@
         <f>C551*C552*1000</f>
         <v>860</v>
       </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E560" s="59" t="s">
         <v>207</v>
       </c>
@@ -11621,6 +13626,11 @@
         <f>C553*C554</f>
         <v>200</v>
       </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="563" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A563" s="68"/>
@@ -11653,6 +13663,11 @@
         <f>C557*0.2*C555</f>
         <v>40</v>
       </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="F565" s="5" t="s">
         <v>541</v>
       </c>
@@ -11664,6 +13679,11 @@
       <c r="C566" s="67">
         <f>-C557*0.2*C556</f>
         <v>-20</v>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="567" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -11697,6 +13717,11 @@
         <f>C563</f>
         <v>200</v>
       </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E569" s="59" t="s">
         <v>224</v>
       </c>
@@ -11709,6 +13734,11 @@
         <f>C567</f>
         <v>20</v>
       </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E570" s="59" t="s">
         <v>226</v>
       </c>
@@ -11721,6 +13751,11 @@
         <f>C558</f>
         <v>30</v>
       </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E571" s="59" t="s">
         <v>204</v>
       </c>
@@ -11733,20 +13768,25 @@
         <f>C560</f>
         <v>860</v>
       </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E572" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="573" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="574" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A574" s="115" t="s">
+      <c r="A574" s="114" t="s">
         <v>666</v>
       </c>
-      <c r="B574" s="115"/>
-      <c r="C574" s="115"/>
-      <c r="D574" s="115"/>
-      <c r="E574" s="115"/>
-      <c r="F574" s="115"/>
+      <c r="B574" s="114"/>
+      <c r="C574" s="114"/>
+      <c r="D574" s="114"/>
+      <c r="E574" s="114"/>
+      <c r="F574" s="114"/>
       <c r="G574" s="55">
         <v>1</v>
       </c>
@@ -11769,6 +13809,11 @@
         <f>Выбросы!C16</f>
         <v>27</v>
       </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E576" s="59" t="s">
         <v>192</v>
       </c>
@@ -11783,6 +13828,11 @@
       <c r="C577" s="4">
         <v>0.08</v>
       </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F577" s="5" t="s">
         <v>543</v>
       </c>
@@ -11795,6 +13845,11 @@
         <f>C584/C579</f>
         <v>3085.7142857142858</v>
       </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E578" s="59" t="s">
         <v>545</v>
       </c>
@@ -11809,6 +13864,11 @@
       <c r="C579" s="89">
         <v>0.7</v>
       </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E579" s="59"/>
       <c r="F579" s="5"/>
     </row>
@@ -11820,6 +13880,11 @@
         <f>MACC!$E$56</f>
         <v>300</v>
       </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E580" s="59" t="s">
         <v>96</v>
       </c>
@@ -11834,6 +13899,11 @@
       <c r="C581" s="66">
         <v>60</v>
       </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E581" s="59" t="s">
         <v>551</v>
       </c>
@@ -11847,6 +13917,11 @@
       </c>
       <c r="C582" s="64">
         <v>25</v>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E582" s="59" t="s">
         <v>204</v>
@@ -11870,6 +13945,11 @@
         <f>C576*C577*1000</f>
         <v>2160</v>
       </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E584" s="59" t="s">
         <v>207</v>
       </c>
@@ -11892,6 +13972,11 @@
         <f>C578*C580/10^3</f>
         <v>925.71428571428567</v>
       </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="587" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B587" s="3" t="s">
@@ -11900,6 +13985,11 @@
       <c r="C587" s="67">
         <f>C586*0.3</f>
         <v>277.71428571428567</v>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="588" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -11933,6 +14023,11 @@
         <f>C578*C581/10^3</f>
         <v>185.14285714285717</v>
       </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="591" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A591" s="68"/>
@@ -11965,6 +14060,11 @@
         <f>C588</f>
         <v>1203.4285714285713</v>
       </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E593" s="59" t="s">
         <v>224</v>
       </c>
@@ -11977,6 +14077,11 @@
         <f>C591</f>
         <v>185.14285714285717</v>
       </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E594" s="59" t="s">
         <v>226</v>
       </c>
@@ -11989,6 +14094,11 @@
         <f>C582</f>
         <v>25</v>
       </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E595" s="59" t="s">
         <v>204</v>
       </c>
@@ -12001,20 +14111,25 @@
         <f>C584</f>
         <v>2160</v>
       </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E596" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="597" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="598" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A598" s="115" t="s">
+      <c r="A598" s="114" t="s">
         <v>556</v>
       </c>
-      <c r="B598" s="115"/>
-      <c r="C598" s="115"/>
-      <c r="D598" s="115"/>
-      <c r="E598" s="115"/>
-      <c r="F598" s="115"/>
+      <c r="B598" s="114"/>
+      <c r="C598" s="114"/>
+      <c r="D598" s="114"/>
+      <c r="E598" s="114"/>
+      <c r="F598" s="114"/>
       <c r="G598" s="96">
         <v>3</v>
       </c>
@@ -12037,6 +14152,11 @@
         <f>Выбросы!C22</f>
         <v>17.8</v>
       </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E600" s="59" t="s">
         <v>192</v>
       </c>
@@ -12051,6 +14171,11 @@
       <c r="C601" s="4">
         <v>0.1</v>
       </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F601" s="5" t="s">
         <v>228</v>
       </c>
@@ -12062,6 +14187,11 @@
       <c r="C602" s="66">
         <v>8500</v>
       </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E602" s="59" t="s">
         <v>559</v>
       </c>
@@ -12076,6 +14206,11 @@
       <c r="C603" s="4">
         <v>0.3</v>
       </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F603" s="5" t="s">
         <v>562</v>
       </c>
@@ -12087,6 +14222,11 @@
       <c r="C604" s="66">
         <v>50</v>
       </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E604" s="59" t="s">
         <v>564</v>
       </c>
@@ -12101,6 +14241,11 @@
       <c r="C605" s="66">
         <v>15</v>
       </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E605" s="59" t="s">
         <v>567</v>
       </c>
@@ -12112,6 +14257,11 @@
       <c r="C606" s="66">
         <v>20</v>
       </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E606" s="59" t="s">
         <v>569</v>
       </c>
@@ -12123,6 +14273,11 @@
       <c r="C607" s="66">
         <v>500</v>
       </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E607" s="59" t="s">
         <v>571</v>
       </c>
@@ -12133,6 +14288,11 @@
       </c>
       <c r="C608" s="64">
         <v>10</v>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E608" s="59" t="s">
         <v>204</v>
@@ -12156,6 +14316,11 @@
         <f>C600*C601*1000</f>
         <v>1780.0000000000002</v>
       </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E610" s="59" t="s">
         <v>207</v>
       </c>
@@ -12168,6 +14333,11 @@
         <f>C602*C603</f>
         <v>2550</v>
       </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E611" s="59" t="s">
         <v>559</v>
       </c>
@@ -12179,6 +14349,11 @@
       <c r="C612" s="65">
         <f>C611*1000/C607</f>
         <v>5100</v>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E612" s="59" t="s">
         <v>478</v>
@@ -12202,6 +14377,11 @@
         <f>C611*1000*C605/10^6</f>
         <v>38.25</v>
       </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="615" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B615" s="3" t="s">
@@ -12210,6 +14390,11 @@
       <c r="C615" s="67">
         <f>C612*C606/10^3</f>
         <v>102</v>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="616" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -12243,6 +14428,11 @@
         <f>C611*1000*C604/10^6</f>
         <v>127.5</v>
       </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="619" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B619" s="3" t="s">
@@ -12251,6 +14441,11 @@
       <c r="C619" s="67">
         <f>C612*5/10^3</f>
         <v>25.5</v>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="F619" s="5" t="s">
         <v>578</v>
@@ -12287,6 +14482,11 @@
         <f>C616</f>
         <v>140.25</v>
       </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E622" s="59" t="s">
         <v>224</v>
       </c>
@@ -12299,6 +14499,11 @@
         <f>C620</f>
         <v>153</v>
       </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E623" s="59" t="s">
         <v>226</v>
       </c>
@@ -12311,6 +14516,11 @@
         <f>C608</f>
         <v>10</v>
       </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E624" s="59" t="s">
         <v>204</v>
       </c>
@@ -12323,20 +14533,25 @@
         <f>C610</f>
         <v>1780.0000000000002</v>
       </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E625" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="626" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="627" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A627" s="115" t="s">
+      <c r="A627" s="114" t="s">
         <v>579</v>
       </c>
-      <c r="B627" s="115"/>
-      <c r="C627" s="115"/>
-      <c r="D627" s="115"/>
-      <c r="E627" s="115"/>
-      <c r="F627" s="115"/>
+      <c r="B627" s="114"/>
+      <c r="C627" s="114"/>
+      <c r="D627" s="114"/>
+      <c r="E627" s="114"/>
+      <c r="F627" s="114"/>
       <c r="G627" s="96">
         <v>3</v>
       </c>
@@ -12356,7 +14571,13 @@
         <v>557</v>
       </c>
       <c r="C629" s="6">
-        <v>42.8</v>
+        <f>Выбросы!C23</f>
+        <v>3.3</v>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="E629" s="59" t="s">
         <v>192</v>
@@ -12372,6 +14593,11 @@
       <c r="C630" s="4">
         <v>0.08</v>
       </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F630" s="5" t="s">
         <v>228</v>
       </c>
@@ -12383,6 +14609,11 @@
       <c r="C631" s="66">
         <v>500</v>
       </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E631" s="59" t="s">
         <v>478</v>
       </c>
@@ -12397,6 +14628,11 @@
       <c r="C632" s="87">
         <v>0.5</v>
       </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E632" s="59" t="s">
         <v>224</v>
       </c>
@@ -12411,6 +14647,11 @@
       <c r="C633" s="66">
         <v>50</v>
       </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E633" s="59" t="s">
         <v>585</v>
       </c>
@@ -12421,6 +14662,11 @@
       </c>
       <c r="C634" s="64">
         <v>15</v>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E634" s="59" t="s">
         <v>204</v>
@@ -12442,7 +14688,12 @@
       </c>
       <c r="C636" s="65">
         <f>C629*C630*1000</f>
-        <v>3424</v>
+        <v>264</v>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E636" s="59" t="s">
         <v>207</v>
@@ -12466,6 +14717,11 @@
         <f>C631*C632</f>
         <v>250</v>
       </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="639" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B639" s="3" t="s">
@@ -12474,6 +14730,11 @@
       <c r="C639" s="67">
         <f>C638*0.2</f>
         <v>50</v>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="640" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -12507,6 +14768,11 @@
         <f>C640*0.04</f>
         <v>12</v>
       </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="643" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B643" s="3" t="s">
@@ -12515,6 +14781,11 @@
       <c r="C643" s="67">
         <f>-C631*C633/10^3</f>
         <v>-25</v>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="644" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -12548,6 +14819,11 @@
         <f>C640</f>
         <v>300</v>
       </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E646" s="59" t="s">
         <v>224</v>
       </c>
@@ -12560,6 +14836,11 @@
         <f>C644</f>
         <v>-13</v>
       </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E647" s="59" t="s">
         <v>226</v>
       </c>
@@ -12572,6 +14853,11 @@
         <f>C634</f>
         <v>15</v>
       </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E648" s="59" t="s">
         <v>204</v>
       </c>
@@ -12582,7 +14868,12 @@
       </c>
       <c r="C649" s="76">
         <f>C636</f>
-        <v>3424</v>
+        <v>264</v>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
       </c>
       <c r="E649" s="59" t="s">
         <v>207</v>
@@ -12590,14 +14881,14 @@
     </row>
     <row r="650" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="651" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A651" s="115" t="s">
+      <c r="A651" s="114" t="s">
         <v>589</v>
       </c>
-      <c r="B651" s="115"/>
-      <c r="C651" s="115"/>
-      <c r="D651" s="115"/>
-      <c r="E651" s="115"/>
-      <c r="F651" s="115"/>
+      <c r="B651" s="114"/>
+      <c r="C651" s="114"/>
+      <c r="D651" s="114"/>
+      <c r="E651" s="114"/>
+      <c r="F651" s="114"/>
       <c r="G651" s="96">
         <v>3</v>
       </c>
@@ -12617,7 +14908,13 @@
         <v>557</v>
       </c>
       <c r="C653" s="6">
-        <v>42.8</v>
+        <f>Выбросы!C25</f>
+        <v>11.6</v>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="E653" s="59" t="s">
         <v>192</v>
@@ -12633,6 +14930,11 @@
       <c r="C654" s="4">
         <v>0.1</v>
       </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F654" s="5" t="s">
         <v>228</v>
       </c>
@@ -12644,6 +14946,11 @@
       <c r="C655" s="66">
         <v>5000</v>
       </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E655" s="59" t="s">
         <v>591</v>
       </c>
@@ -12658,6 +14965,11 @@
       <c r="C656" s="66">
         <v>30</v>
       </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E656" s="59" t="s">
         <v>99</v>
       </c>
@@ -12672,6 +14984,11 @@
       <c r="C657" s="66">
         <v>15</v>
       </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E657" s="59" t="s">
         <v>596</v>
       </c>
@@ -12685,6 +15002,11 @@
       </c>
       <c r="C658" s="64">
         <v>10</v>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E658" s="59" t="s">
         <v>204</v>
@@ -12706,7 +15028,12 @@
       </c>
       <c r="C660" s="65">
         <f>C653*C654*1000</f>
-        <v>4280</v>
+        <v>1160</v>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E660" s="59" t="s">
         <v>207</v>
@@ -12730,6 +15057,11 @@
         <f>C655*C656*1000/10^6</f>
         <v>150</v>
       </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="663" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B663" s="3" t="s">
@@ -12738,6 +15070,11 @@
       <c r="C663" s="67">
         <f>30</f>
         <v>30</v>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="F663" s="5" t="s">
         <v>224</v>
@@ -12774,6 +15111,11 @@
         <f>C664*0.05</f>
         <v>9</v>
       </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="667" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B667" s="3" t="s">
@@ -12782,6 +15124,11 @@
       <c r="C667" s="67">
         <f>-C655*C657*1000/10^6</f>
         <v>-75</v>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="668" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -12815,6 +15162,11 @@
         <f>C664</f>
         <v>180</v>
       </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E670" s="59" t="s">
         <v>224</v>
       </c>
@@ -12827,6 +15179,11 @@
         <f>C668</f>
         <v>-66</v>
       </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E671" s="59" t="s">
         <v>226</v>
       </c>
@@ -12839,6 +15196,11 @@
         <f>C658</f>
         <v>10</v>
       </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E672" s="59" t="s">
         <v>204</v>
       </c>
@@ -12849,7 +15211,12 @@
       </c>
       <c r="C673" s="76">
         <f>C660</f>
-        <v>4280</v>
+        <v>1160</v>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
       </c>
       <c r="E673" s="59" t="s">
         <v>207</v>
@@ -12857,14 +15224,14 @@
     </row>
     <row r="674" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="675" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A675" s="115" t="s">
+      <c r="A675" s="114" t="s">
         <v>602</v>
       </c>
-      <c r="B675" s="115"/>
-      <c r="C675" s="115"/>
-      <c r="D675" s="115"/>
-      <c r="E675" s="115"/>
-      <c r="F675" s="115"/>
+      <c r="B675" s="114"/>
+      <c r="C675" s="114"/>
+      <c r="D675" s="114"/>
+      <c r="E675" s="114"/>
+      <c r="F675" s="114"/>
       <c r="G675" s="96">
         <v>3</v>
       </c>
@@ -12884,7 +15251,13 @@
         <v>557</v>
       </c>
       <c r="C677" s="6">
-        <v>42.8</v>
+        <f>Выбросы!C25</f>
+        <v>11.6</v>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
       </c>
       <c r="E677" s="59" t="s">
         <v>192</v>
@@ -12900,6 +15273,11 @@
       <c r="C678" s="4">
         <v>0.05</v>
       </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F678" s="5" t="s">
         <v>228</v>
       </c>
@@ -12911,6 +15289,11 @@
       <c r="C679" s="66">
         <v>10000</v>
       </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E679" s="59" t="s">
         <v>591</v>
       </c>
@@ -12925,6 +15308,11 @@
       <c r="C680" s="66">
         <v>20</v>
       </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E680" s="59" t="s">
         <v>99</v>
       </c>
@@ -12939,6 +15327,11 @@
       <c r="C681" s="66">
         <v>5</v>
       </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E681" s="59" t="s">
         <v>596</v>
       </c>
@@ -12952,6 +15345,11 @@
       </c>
       <c r="C682" s="64">
         <v>20</v>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E682" s="59" t="s">
         <v>204</v>
@@ -12973,7 +15371,12 @@
       </c>
       <c r="C684" s="65">
         <f>C677*C678*1000</f>
-        <v>2140</v>
+        <v>580</v>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E684" s="59" t="s">
         <v>207</v>
@@ -12997,6 +15400,11 @@
         <f>C679*C680*1000/10^6</f>
         <v>200</v>
       </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="687" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B687" s="3" t="s">
@@ -13005,6 +15413,11 @@
       <c r="C687" s="67">
         <f>C686*0.15</f>
         <v>30</v>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="688" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -13038,6 +15451,11 @@
         <f>C688*0.02</f>
         <v>4.6000000000000005</v>
       </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="691" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B691" s="3" t="s">
@@ -13046,6 +15464,11 @@
       <c r="C691" s="67">
         <f>-C679*C681*1000/10^6</f>
         <v>-50</v>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="692" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -13079,6 +15502,11 @@
         <f>C688</f>
         <v>230</v>
       </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E694" s="59" t="s">
         <v>224</v>
       </c>
@@ -13091,6 +15519,11 @@
         <f>C692</f>
         <v>-45.4</v>
       </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E695" s="59" t="s">
         <v>226</v>
       </c>
@@ -13103,6 +15536,11 @@
         <f>C682</f>
         <v>20</v>
       </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E696" s="59" t="s">
         <v>204</v>
       </c>
@@ -13113,7 +15551,12 @@
       </c>
       <c r="C697" s="76">
         <f>C684</f>
-        <v>2140</v>
+        <v>580</v>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
       </c>
       <c r="E697" s="59" t="s">
         <v>207</v>
@@ -13121,14 +15564,14 @@
     </row>
     <row r="698" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="699" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A699" s="115" t="s">
+      <c r="A699" s="114" t="s">
         <v>613</v>
       </c>
-      <c r="B699" s="115"/>
-      <c r="C699" s="115"/>
-      <c r="D699" s="115"/>
-      <c r="E699" s="115"/>
-      <c r="F699" s="115"/>
+      <c r="B699" s="114"/>
+      <c r="C699" s="114"/>
+      <c r="D699" s="114"/>
+      <c r="E699" s="114"/>
+      <c r="F699" s="114"/>
       <c r="G699" s="55">
         <v>1</v>
       </c>
@@ -13151,6 +15594,11 @@
         <f>Выбросы!C28</f>
         <v>3.6</v>
       </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E701" s="59" t="s">
         <v>192</v>
       </c>
@@ -13165,6 +15613,11 @@
       <c r="C702" s="4">
         <v>0.1</v>
       </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F702" s="5" t="s">
         <v>228</v>
       </c>
@@ -13176,6 +15629,11 @@
       <c r="C703" s="66">
         <v>20</v>
       </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E703" s="59" t="s">
         <v>478</v>
       </c>
@@ -13190,6 +15648,11 @@
       <c r="C704" s="66">
         <v>5</v>
       </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E704" s="59" t="s">
         <v>618</v>
       </c>
@@ -13202,6 +15665,11 @@
         <f>C712*C706*10^-6</f>
         <v>10.011428571428574</v>
       </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E705" s="59" t="s">
         <v>619</v>
       </c>
@@ -13217,6 +15685,11 @@
         <f>MACC!$E$38</f>
         <v>50</v>
       </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
+      </c>
       <c r="E706" s="59" t="s">
         <v>59</v>
       </c>
@@ -13229,6 +15702,11 @@
       <c r="C707" s="66">
         <v>1400</v>
       </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E707" s="59" t="s">
         <v>72</v>
       </c>
@@ -13242,6 +15720,11 @@
         <f>C715*10^3/C707</f>
         <v>28.571428571428573</v>
       </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E708" s="59" t="s">
         <v>209</v>
       </c>
@@ -13253,6 +15736,11 @@
       </c>
       <c r="C709" s="64">
         <v>20</v>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E709" s="59" t="s">
         <v>204</v>
@@ -13276,6 +15764,11 @@
         <f>C701*C702*1000</f>
         <v>360.00000000000006</v>
       </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E711" s="59" t="s">
         <v>207</v>
       </c>
@@ -13287,6 +15780,11 @@
       <c r="C712" s="65">
         <f>C708*0.8*8760</f>
         <v>200228.57142857148</v>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E712" s="59" t="s">
         <v>625</v>
@@ -13310,6 +15808,11 @@
         <f>C703*C704</f>
         <v>100</v>
       </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="715" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B715" s="3" t="s">
@@ -13318,6 +15821,11 @@
       <c r="C715" s="67">
         <f>C714*0.4</f>
         <v>40</v>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="716" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -13351,6 +15859,11 @@
         <f>C716*0.04</f>
         <v>5.6000000000000005</v>
       </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="719" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B719" s="3" t="s">
@@ -13359,6 +15872,11 @@
       <c r="C719" s="67">
         <f>-C705</f>
         <v>-10.011428571428574</v>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
     </row>
     <row r="720" spans="1:6" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
@@ -13392,6 +15910,11 @@
         <f>C716</f>
         <v>140</v>
       </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E722" s="59" t="s">
         <v>224</v>
       </c>
@@ -13404,6 +15927,11 @@
         <f>C720</f>
         <v>-4.4114285714285737</v>
       </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E723" s="59" t="s">
         <v>226</v>
       </c>
@@ -13416,6 +15944,11 @@
         <f>C709</f>
         <v>20</v>
       </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E724" s="59" t="s">
         <v>204</v>
       </c>
@@ -13428,25 +15961,30 @@
         <f>C711</f>
         <v>360.00000000000006</v>
       </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E725" s="59" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="726" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="727" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A727" s="115" t="s">
+      <c r="A727" s="114" t="s">
         <v>628</v>
       </c>
-      <c r="B727" s="115"/>
-      <c r="C727" s="115"/>
-      <c r="D727" s="115"/>
-      <c r="E727" s="115"/>
-      <c r="F727" s="115"/>
+      <c r="B727" s="114"/>
+      <c r="C727" s="114"/>
+      <c r="D727" s="114"/>
+      <c r="E727" s="114"/>
+      <c r="F727" s="114"/>
       <c r="G727" s="94">
         <v>2</v>
       </c>
     </row>
-    <row r="728" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A728" s="56"/>
       <c r="B728" s="57" t="s">
         <v>190</v>
@@ -13456,7 +15994,7 @@
       <c r="E728" s="56"/>
       <c r="F728" s="56"/>
     </row>
-    <row r="729" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B729" s="3" t="s">
         <v>614</v>
       </c>
@@ -13464,6 +16002,11 @@
         <f>Выбросы!C29</f>
         <v>3.2</v>
       </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E729" s="59" t="s">
         <v>192</v>
       </c>
@@ -13471,24 +16014,34 @@
         <v>193</v>
       </c>
     </row>
-    <row r="730" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B730" s="3" t="s">
         <v>194</v>
       </c>
       <c r="C730" s="4">
         <v>0.1</v>
       </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F730" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="731" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B731" s="3" t="s">
         <v>629</v>
       </c>
       <c r="C731" s="66">
         <v>15</v>
       </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E731" s="59" t="s">
         <v>478</v>
       </c>
@@ -13496,13 +16049,18 @@
         <v>616</v>
       </c>
     </row>
-    <row r="732" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B732" s="3" t="s">
-        <v>198</v>
+        <v>670</v>
       </c>
       <c r="C732" s="66">
         <v>10</v>
       </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E732" s="59" t="s">
         <v>630</v>
       </c>
@@ -13510,29 +16068,39 @@
         <v>631</v>
       </c>
     </row>
-    <row r="733" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B733" s="3" t="s">
         <v>632</v>
       </c>
       <c r="C733" s="66">
         <v>1</v>
       </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E733" s="59" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="734" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B734" s="3" t="s">
         <v>203</v>
       </c>
       <c r="C734" s="64">
         <v>25</v>
       </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E734" s="59" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="735" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A735" s="56"/>
       <c r="B735" s="57" t="s">
         <v>205</v>
@@ -13542,7 +16110,7 @@
       <c r="E735" s="56"/>
       <c r="F735" s="56"/>
     </row>
-    <row r="736" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B736" s="3" t="s">
         <v>206</v>
       </c>
@@ -13550,11 +16118,16 @@
         <f>C729*C730*1000</f>
         <v>320.00000000000006</v>
       </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E736" s="59" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="737" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A737" s="56"/>
       <c r="B737" s="57" t="s">
         <v>211</v>
@@ -13564,7 +16137,7 @@
       <c r="E737" s="56"/>
       <c r="F737" s="56"/>
     </row>
-    <row r="738" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B738" s="3" t="s">
         <v>634</v>
       </c>
@@ -13572,8 +16145,13 @@
         <f>C731*C732</f>
         <v>150</v>
       </c>
-    </row>
-    <row r="739" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
+    </row>
+    <row r="739" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A739" s="68"/>
       <c r="B739" s="69" t="s">
         <v>215</v>
@@ -13586,7 +16164,7 @@
       <c r="E739" s="68"/>
       <c r="F739" s="68"/>
     </row>
-    <row r="740" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A740" s="56"/>
       <c r="B740" s="57" t="s">
         <v>216</v>
@@ -13596,7 +16174,7 @@
       <c r="E740" s="56"/>
       <c r="F740" s="56"/>
     </row>
-    <row r="741" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B741" s="3" t="s">
         <v>217</v>
       </c>
@@ -13604,8 +16182,13 @@
         <f>C739*0.03</f>
         <v>4.5</v>
       </c>
-    </row>
-    <row r="742" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
+    </row>
+    <row r="742" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B742" s="3" t="s">
         <v>635</v>
       </c>
@@ -13613,8 +16196,13 @@
         <f>-C731*C733</f>
         <v>-15</v>
       </c>
-    </row>
-    <row r="743" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
+    </row>
+    <row r="743" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A743" s="68"/>
       <c r="B743" s="69" t="s">
         <v>221</v>
@@ -13627,7 +16215,7 @@
       <c r="E743" s="68"/>
       <c r="F743" s="68"/>
     </row>
-    <row r="744" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A744" s="56"/>
       <c r="B744" s="57" t="s">
         <v>222</v>
@@ -13637,7 +16225,7 @@
       <c r="E744" s="56"/>
       <c r="F744" s="56"/>
     </row>
-    <row r="745" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B745" s="73" t="s">
         <v>223</v>
       </c>
@@ -13645,11 +16233,16 @@
         <f>C739</f>
         <v>150</v>
       </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E745" s="59" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="746" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B746" s="73" t="s">
         <v>225</v>
       </c>
@@ -13657,11 +16250,16 @@
         <f>C743</f>
         <v>-10.5</v>
       </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E746" s="59" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="747" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B747" s="73" t="s">
         <v>203</v>
       </c>
@@ -13669,11 +16267,16 @@
         <f>C734</f>
         <v>25</v>
       </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E747" s="59" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="748" spans="1:7" ht="15" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:7" ht="15" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B748" s="73" t="s">
         <v>206</v>
       </c>
@@ -13681,20 +16284,24 @@
         <f>C736</f>
         <v>320.00000000000006</v>
       </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E748" s="59" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="749" spans="1:7" collapsed="1" x14ac:dyDescent="0.35"/>
     <row r="750" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A750" s="114" t="s">
+      <c r="A750" s="115" t="s">
         <v>636</v>
       </c>
-      <c r="B750" s="114"/>
-      <c r="C750" s="114"/>
-      <c r="D750" s="114"/>
-      <c r="E750" s="114"/>
-      <c r="F750" s="114"/>
+      <c r="B750" s="115"/>
+      <c r="C750" s="115"/>
+      <c r="D750" s="115"/>
+      <c r="E750" s="115"/>
+      <c r="F750" s="115"/>
       <c r="G750" s="55">
         <v>1</v>
       </c>
@@ -13717,6 +16324,11 @@
         <f>Выбросы!C26</f>
         <v>4.13</v>
       </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
       <c r="E752" s="98" t="s">
         <v>192</v>
       </c>
@@ -13731,6 +16343,11 @@
       <c r="C753" s="99">
         <v>1000</v>
       </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E753" s="98" t="s">
         <v>591</v>
       </c>
@@ -13745,6 +16362,11 @@
       <c r="C754" s="100">
         <v>0.7</v>
       </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="F754" s="21" t="s">
         <v>642</v>
       </c>
@@ -13756,6 +16378,11 @@
       <c r="C755" s="101">
         <v>3</v>
       </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E755" s="98" t="s">
         <v>644</v>
       </c>
@@ -13770,6 +16397,11 @@
       <c r="C756" s="61">
         <f>MACC!$E$57</f>
         <v>2000</v>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>IN-G</t>
+        </is>
       </c>
       <c r="E756" s="98" t="s">
         <v>99</v>
@@ -13791,6 +16423,11 @@
       <c r="C758" s="99">
         <v>100</v>
       </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
+      </c>
       <c r="E758" s="98" t="s">
         <v>596</v>
       </c>
@@ -13804,6 +16441,11 @@
       </c>
       <c r="C759" s="102">
         <v>30</v>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>IN-L</t>
+        </is>
       </c>
       <c r="E759" s="98" t="s">
         <v>204</v>
@@ -13830,6 +16472,11 @@
         <f>C753*C754</f>
         <v>700</v>
       </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
       <c r="E761" s="98" t="s">
         <v>591</v>
       </c>
@@ -13841,6 +16488,11 @@
       <c r="C762" s="103">
         <f>C761*C755</f>
         <v>2100</v>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="E762" s="98" t="s">
         <v>654</v>
@@ -13867,6 +16519,11 @@
         <f>C753*C756/10^3</f>
         <v>2000</v>
       </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="765" spans="1:6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B765" s="12"/>
@@ -13879,6 +16536,11 @@
       <c r="C766" s="104">
         <f>(C764+C765)*0.1</f>
         <v>200</v>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="F766" s="21" t="s">
         <v>658</v>
@@ -13915,6 +16577,11 @@
         <f>C753*C758/10^3</f>
         <v>100</v>
       </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
+      </c>
     </row>
     <row r="770" spans="1:6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B770" s="12" t="s">
@@ -13923,6 +16590,11 @@
       <c r="C770" s="104">
         <f>C767*0.005</f>
         <v>11</v>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>CALC</t>
+        </is>
       </c>
       <c r="F770" s="21" t="s">
         <v>662</v>
@@ -13959,6 +16631,11 @@
         <f>C767</f>
         <v>2200</v>
       </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E773" s="98" t="s">
         <v>224</v>
       </c>
@@ -13971,6 +16648,11 @@
         <f>C771</f>
         <v>111</v>
       </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E774" s="98" t="s">
         <v>226</v>
       </c>
@@ -13983,6 +16665,11 @@
         <f>C759</f>
         <v>30</v>
       </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E775" s="98" t="s">
         <v>204</v>
       </c>
@@ -13995,6 +16682,11 @@
         <f>C762</f>
         <v>2100</v>
       </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>OUT</t>
+        </is>
+      </c>
       <c r="E776" s="98" t="s">
         <v>654</v>
       </c>
@@ -14002,32 +16694,32 @@
     <row r="777" spans="1:6" collapsed="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A177:F177"/>
-    <mergeCell ref="A207:F207"/>
-    <mergeCell ref="A245:F245"/>
-    <mergeCell ref="A282:F282"/>
-    <mergeCell ref="A307:F307"/>
-    <mergeCell ref="A340:F340"/>
-    <mergeCell ref="A378:F378"/>
-    <mergeCell ref="A409:F409"/>
-    <mergeCell ref="A448:F448"/>
-    <mergeCell ref="A474:F474"/>
-    <mergeCell ref="A499:F499"/>
-    <mergeCell ref="A523:F523"/>
-    <mergeCell ref="A549:F549"/>
-    <mergeCell ref="A574:F574"/>
-    <mergeCell ref="A598:F598"/>
     <mergeCell ref="A750:F750"/>
     <mergeCell ref="A627:F627"/>
     <mergeCell ref="A651:F651"/>
     <mergeCell ref="A675:F675"/>
     <mergeCell ref="A699:F699"/>
     <mergeCell ref="A727:F727"/>
+    <mergeCell ref="A499:F499"/>
+    <mergeCell ref="A523:F523"/>
+    <mergeCell ref="A549:F549"/>
+    <mergeCell ref="A574:F574"/>
+    <mergeCell ref="A598:F598"/>
+    <mergeCell ref="A340:F340"/>
+    <mergeCell ref="A378:F378"/>
+    <mergeCell ref="A409:F409"/>
+    <mergeCell ref="A448:F448"/>
+    <mergeCell ref="A474:F474"/>
+    <mergeCell ref="A177:F177"/>
+    <mergeCell ref="A207:F207"/>
+    <mergeCell ref="A245:F245"/>
+    <mergeCell ref="A282:F282"/>
+    <mergeCell ref="A307:F307"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A135:F135"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/MACC_KZ_29052026_rev.xlsx
+++ b/MACC_KZ_29052026_rev.xlsx
@@ -963,7 +963,7 @@
     <t>Паровая+водогрейная котельная</t>
   </si>
   <si>
-    <t>Тепловая мощности ТЭЦ</t>
+    <t>Тепловая мощность ТЭЦ</t>
   </si>
   <si>
     <t>выработк</t>
@@ -1029,7 +1029,7 @@
     <t>[1.A.1-6] Тепловые насосы для централизованного теплоснабжения</t>
   </si>
   <si>
-    <t>Общий объем проивзодства тепла</t>
+    <t>Общий объем производства тепла</t>
   </si>
   <si>
     <t>тыс Гкал</t>
